--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 13.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 14.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 13.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 14.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 14.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 15.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 14.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 15.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 15.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 16.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 15.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 16.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 16.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 17.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 16.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 17.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 17.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 18.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 17.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 18.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 18.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 19.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 18.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 19.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 19.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 20.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 19.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 20.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 20.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 21.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 20.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 21.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 21.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 22.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 21.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 22.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 22.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 23.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 22.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 23.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 23.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 24.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 23.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 24.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 24.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 25.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 24.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 25.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 25.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 26.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 25.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 26.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 26.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 27.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 26.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 27.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 27.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 28.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 27.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 28.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 28.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 29.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 28.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 29.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 29.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 30.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 29.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 30.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -330,7 +330,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Брецель-дог (20шт)</a:t>
+              <a:t>Сосиска в тесте (30шт гофра)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -361,12 +361,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$5:$J$5</f>
+              <f>'Цены по месяцам'!$C$5:$K$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -431,7 +431,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Пирожок с картофелем (30 шт гофра)</a:t>
+              <a:t>Курица с сыром с рисом и паутини (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -462,12 +462,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$149:$J$149</f>
+              <f>'Цены по месяцам'!$C$149:$K$149</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -532,7 +532,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Маффин шоколадный (24шт)</a:t>
+              <a:t>Пирожок с картофелем (30 шт гофра)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -563,12 +563,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$165:$J$165</f>
+              <f>'Цены по месяцам'!$C$165:$K$165</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -664,12 +664,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$181:$J$181</f>
+              <f>'Цены по месяцам'!$C$181:$K$181</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -734,7 +734,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Пирожок с капустой (30 шт гофра)</a:t>
+              <a:t>Манты с говядиной (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -765,12 +765,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$197:$J$197</f>
+              <f>'Цены по месяцам'!$C$197:$K$197</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -835,7 +835,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Манты с говядиной (1порц)</a:t>
+              <a:t>Шницель куриный с картофельным пюре (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -866,12 +866,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$213:$J$213</f>
+              <f>'Цены по месяцам'!$C$213:$K$213</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -936,7 +936,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Сочник творожный (30шт гофра )</a:t>
+              <a:t>Пирожок с капустой (30 шт гофра)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -967,12 +967,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$229:$J$229</f>
+              <f>'Цены по месяцам'!$C$229:$K$229</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1037,7 +1037,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Бризоль с рисом (1порц)</a:t>
+              <a:t>Клаб Сэндвич с курицей (1шт)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1068,12 +1068,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$245:$J$245</f>
+              <f>'Цены по месяцам'!$C$245:$K$245</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1169,12 +1169,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$261:$J$261</f>
+              <f>'Цены по месяцам'!$C$261:$K$261</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1239,7 +1239,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Самса с говядиной (30 шт гофра)</a:t>
+              <a:t>Курица с сыром с пастой фузилли (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1270,12 +1270,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$277:$J$277</f>
+              <f>'Цены по месяцам'!$C$277:$K$277</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1340,7 +1340,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Самса с курицей (30шт гофра )</a:t>
+              <a:t>Курица с сыром и гречкой (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1371,12 +1371,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$293:$J$293</f>
+              <f>'Цены по месяцам'!$C$293:$K$293</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1441,7 +1441,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Сосиска в тесте (30шт гофра)</a:t>
+              <a:t>Брецель-дог (20шт)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1472,12 +1472,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$21:$J$21</f>
+              <f>'Цены по месяцам'!$C$21:$K$21</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1542,7 +1542,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Круассан с индейкой (1шт)</a:t>
+              <a:t>Сочник творожный (30шт гофра )</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1573,12 +1573,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$309:$J$309</f>
+              <f>'Цены по месяцам'!$C$309:$K$309</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1674,12 +1674,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$37:$J$37</f>
+              <f>'Цены по месяцам'!$C$37:$K$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1775,12 +1775,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$53:$J$53</f>
+              <f>'Цены по месяцам'!$C$53:$K$53</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1845,7 +1845,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Пирожок с курицей и сыром (30 шт гофра)</a:t>
+              <a:t>Кимпаб с тунцом (1шт)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1876,12 +1876,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$69:$J$69</f>
+              <f>'Цены по месяцам'!$C$69:$K$69</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1946,7 +1946,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Кимпаб с тунцом (1шт)</a:t>
+              <a:t>Пирожок с курицей и сыром (30 шт гофра)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1977,12 +1977,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$85:$J$85</f>
+              <f>'Цены по месяцам'!$C$85:$K$85</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2078,12 +2078,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$101:$J$101</f>
+              <f>'Цены по месяцам'!$C$101:$K$101</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2148,7 +2148,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Курица с сыром и картофельным пюре (1порц)</a:t>
+              <a:t>Маффин шоколадный (24шт)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2179,12 +2179,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$117:$J$117</f>
+              <f>'Цены по месяцам'!$C$117:$K$117</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2249,7 +2249,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Курица с сыром с рисом и паутини (1порц)</a:t>
+              <a:t>Курица с сыром и картофельным пюре (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2280,12 +2280,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Цены по месяцам'!$C$4:$J$4</f>
+              <f>'Цены по месяцам'!$C$4:$K$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Цены по месяцам'!$C$133:$J$133</f>
+              <f>'Цены по месяцам'!$C$133:$K$133</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 30.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 01.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Брецель-дог (20шт)</t>
+          <t>Сосиска в тесте (30шт гофра)</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -3259,31 +3259,31 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>11469333</v>
+        <v>9409940</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1627</v>
+        <v>995</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>7048</v>
+        <v>9454</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>-0.005144146725738707</v>
+        <v>0.01983196557667033</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.53968</v>
+        <v>0.5969786552575863</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>0.6096274315858885</v>
+        <v>0.2631133671742809</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="M8" s="10">
         <f>ROUND(F8*(1+L8),0)</f>
@@ -3311,19 +3311,19 @@
       </c>
       <c r="S8" s="14" t="inlineStr">
         <is>
-          <t>за 6 мес цена упала на 0.5% при ориентире 4.0%; берут на 61% больше</t>
+          <t>за 9 мес цена выросла на 2.0% при ориентире 6.0%</t>
         </is>
       </c>
       <c r="T8" s="14" t="inlineStr">
         <is>
-          <t>Упак Брецель-дог (20шт) · RP* Упак Брецель-дог (20шт)</t>
+          <t>RP* Упак Сосиска в тесте  готов СМ (30шт гофра) · Упак Сосиска в тесте  готов СМ (30шт гофра)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>Сосиска в тесте (30шт гофра)</t>
+          <t>Брецель-дог (20шт)</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -3337,31 +3337,31 @@
         </is>
       </c>
       <c r="D9" s="16" t="n">
-        <v>10024686</v>
+        <v>9173640</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>1070</v>
+        <v>1296</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>9366</v>
+        <v>7077</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>0.01606738290323895</v>
+        <v>0.00286179319379154</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.5969786552575863</v>
+        <v>0.53968</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>0.402183406113537</v>
+        <v>-0.05515063168124401</v>
       </c>
       <c r="K9" s="17" t="n">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="M9" s="16">
         <f>ROUND(F9*(1+L9),0)</f>
@@ -3389,12 +3389,12 @@
       </c>
       <c r="S9" s="19" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 1.6% при ориентире 5.3%; берут на 40% больше</t>
+          <t>за 7 мес цена выросла на 0.3% при ориентире 4.7%</t>
         </is>
       </c>
       <c r="T9" s="19" t="inlineStr">
         <is>
-          <t>RP* Упак Сосиска в тесте  готов СМ (30шт гофра) · Упак Сосиска в тесте  готов СМ (30шт гофра)</t>
+          <t>Упак Брецель-дог (20шт) · RP* Упак Брецель-дог (20шт)</t>
         </is>
       </c>
     </row>
@@ -3415,25 +3415,25 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>6107960</v>
+        <v>6031604</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>6997</v>
+        <v>6799</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>873</v>
+        <v>887</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.09871479706694419</v>
+        <v>0.1148493472172052</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="11" t="n">
         <v>0.543</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>0.2044411292173514</v>
+        <v>0.05628916161773079</v>
       </c>
       <c r="K10" s="11" t="n">
         <v>0</v>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="S10" s="14" t="inlineStr">
         <is>
-          <t>цену уже подняли на 9.9% — этого хватает</t>
+          <t>цену уже подняли на 11.5% — этого хватает</t>
         </is>
       </c>
       <c r="T10" s="14" t="inlineStr">
@@ -3493,25 +3493,25 @@
         </is>
       </c>
       <c r="D11" s="16" t="n">
-        <v>5381606</v>
+        <v>5428360</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>5162</v>
+        <v>5044</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>1042</v>
+        <v>1076</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.143794876713911</v>
+        <v>0.1637387262499683</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I11" s="17" t="n">
         <v>0.476</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>0.05843357025697093</v>
+        <v>-0.002570694087403624</v>
       </c>
       <c r="K11" s="17" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="S11" s="19" t="inlineStr">
         <is>
-          <t>цену уже подняли на 14.4% — этого хватает</t>
+          <t>цену уже подняли на 16.4% — этого хватает</t>
         </is>
       </c>
       <c r="T11" s="19" t="inlineStr">
@@ -3557,45 +3557,45 @@
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Пирожок с курицей и сыром (30 шт гофра)</t>
+          <t>Кимпаб с тунцом (1шт)</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Выпечка_</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>1 — сейчас</t>
+          <t>Япония</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>— не трогать</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>5162738</v>
+        <v>5232716</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>980</v>
+        <v>5318</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>5270</v>
+        <v>984</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.006092178303630735</v>
+        <v>0.12493049455731</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.4993299298854</v>
+        <v>0.546</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>0.4364613880742911</v>
+        <v>0.07891533675953477</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="M12" s="10">
         <f>ROUND(F12*(1+L12),0)</f>
@@ -3623,57 +3623,57 @@
       </c>
       <c r="S12" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 0.6% при ориентире 5.3%; берут на 44% больше</t>
+          <t>цену уже подняли на 12.5% — этого хватает</t>
         </is>
       </c>
       <c r="T12" s="14" t="inlineStr">
         <is>
-          <t>RP* Упак Пирожок с курицей и сыром готов СМ (30 шт гофра) · Упак Пирожок с курицей и сыром готов СМ (30 шт гофра)</t>
+          <t>Упак Кимпаб с тунцом (1шт)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Кимпаб с тунцом (1шт)</t>
+          <t>Пирожок с курицей и сыром (30 шт гофра)</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Япония</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>— не трогать</t>
+          <t>Выпечка_</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>2 — следом</t>
         </is>
       </c>
       <c r="D13" s="16" t="n">
-        <v>5104472</v>
+        <v>4740440</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>5379</v>
+        <v>894</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>949</v>
+        <v>5304</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.1144551028227871</v>
+        <v>0.007177689972479362</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>0.546</v>
+        <v>0.4993299298854</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>0.2232582821620803</v>
+        <v>0.2563261480787253</v>
       </c>
       <c r="K13" s="17" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="M13" s="16">
         <f>ROUND(F13*(1+L13),0)</f>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="S13" s="19" t="inlineStr">
         <is>
-          <t>цену уже подняли на 11.4% — этого хватает</t>
+          <t>за 9 мес цена выросла на 0.7% при ориентире 6.0%</t>
         </is>
       </c>
       <c r="T13" s="19" t="inlineStr">
         <is>
-          <t>Упак Кимпаб с тунцом (1шт)</t>
+          <t>RP* Упак Пирожок с курицей и сыром готов СМ (30 шт гофра) · Упак Пирожок с курицей и сыром готов СМ (30 шт гофра)</t>
         </is>
       </c>
     </row>
@@ -3727,25 +3727,25 @@
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>4336019</v>
+        <v>4461715</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>5350</v>
+        <v>5326</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>810</v>
+        <v>838</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.09497220501137482</v>
+        <v>0.1164652186153825</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I14" s="11" t="n">
         <v>0.498</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>0.1162887745166225</v>
+        <v>0.01331895731591293</v>
       </c>
       <c r="K14" s="11" t="n">
         <v>0</v>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="S14" s="14" t="inlineStr">
         <is>
-          <t>цену уже подняли на 9.5% — этого хватает</t>
+          <t>цену уже подняли на 11.6% — этого хватает</t>
         </is>
       </c>
       <c r="T14" s="14" t="inlineStr">
@@ -3791,45 +3791,45 @@
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Курица с сыром и картофельным пюре (1порц)</t>
+          <t>Маффин шоколадный (24шт)</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Горячее</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>— не трогать</t>
+          <t>Выпечка_</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>1 — сейчас</t>
         </is>
       </c>
       <c r="D15" s="16" t="n">
-        <v>4293422</v>
+        <v>4179161</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>3814</v>
+        <v>570</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>1126</v>
+        <v>7332</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>0.07968634845642675</v>
+        <v>-0.003665392881112228</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.583</v>
+        <v>0.4937349562821021</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>0.1776268395595348</v>
+        <v>0.3317757009345794</v>
       </c>
       <c r="K15" s="17" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="M15" s="16">
         <f>ROUND(F15*(1+L15),0)</f>
@@ -3857,19 +3857,19 @@
       </c>
       <c r="S15" s="19" t="inlineStr">
         <is>
-          <t>признаков отставания цены нет</t>
+          <t>за 9 мес цена упала на 0.4% при ориентире 6.0%; берут на 33% больше</t>
         </is>
       </c>
       <c r="T15" s="19" t="inlineStr">
         <is>
-          <t>Упак Курица с сыром и картофельным пюре (1порц)</t>
+          <t>Упак Маффин шоколадный (24шт) · RP* Упак Маффин шоколадный (24шт)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Курица с сыром с рисом и паутини (1порц)</t>
+          <t>Курица с сыром и картофельным пюре (1порц)</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -3883,25 +3883,25 @@
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>3800654</v>
+        <v>4018098</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>3515</v>
+        <v>3572</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1081</v>
+        <v>1125</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.07050092845465161</v>
+        <v>0.07968634845642675</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>0.589</v>
+        <v>0.583</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>0.1870989530563998</v>
+        <v>-0.05502160303324222</v>
       </c>
       <c r="K16" s="11" t="n">
         <v>0</v>
@@ -3940,52 +3940,52 @@
       </c>
       <c r="T16" s="14" t="inlineStr">
         <is>
-          <t>Упак Курица с сыром с рисом и паутини (1порц)</t>
+          <t>Упак Курица с сыром и картофельным пюре (1порц)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Пирожок с картофелем (30 шт гофра)</t>
+          <t>Курица с сыром с рисом и паутини (1порц)</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Выпечка_</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>2 — следом</t>
+          <t>Горячее</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>— не трогать</t>
         </is>
       </c>
       <c r="D17" s="16" t="n">
-        <v>3782740</v>
+        <v>3602692</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>826</v>
+        <v>3266</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>4580</v>
+        <v>1103</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.0742387783059526</v>
+        <v>0.08149746441462312</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>0.6046347372539482</v>
+        <v>0.589</v>
       </c>
       <c r="J17" s="17" t="n">
-        <v>0.7662152530292229</v>
+        <v>-0.03315571343990531</v>
       </c>
       <c r="K17" s="17" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="M17" s="16">
         <f>ROUND(F17*(1+L17),0)</f>
@@ -4013,19 +4013,19 @@
       </c>
       <c r="S17" s="19" t="inlineStr">
         <is>
-          <t>берут на 77% больше</t>
+          <t>признаков отставания цены нет</t>
         </is>
       </c>
       <c r="T17" s="19" t="inlineStr">
         <is>
-          <t>RP* Упак Пирожок с картофелем готов СМ (30 шт гофра) · Упак Пирожок с картофелем готов СМ (30 шт гофра)</t>
+          <t>Упак Курица с сыром с рисом и паутини (1порц)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Маффин шоколадный (24шт)</t>
+          <t>Пирожок с картофелем (30 шт гофра)</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -4033,37 +4033,37 @@
           <t>Выпечка_</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>2 — следом</t>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>— не трогать</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>3539168</v>
+        <v>3563970</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>482</v>
+        <v>743</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>7343</v>
+        <v>4799</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>-0.003665392881112228</v>
+        <v>0.08443270354943057</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>0.4937349562821021</v>
+        <v>0.6046347372539482</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>0.130570758405004</v>
+        <v>0.3890274314214464</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="M18" s="10">
         <f>ROUND(F18*(1+L18),0)</f>
@@ -4091,12 +4091,12 @@
       </c>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена упала на 0.4% при ориентире 5.3%</t>
+          <t>цену уже подняли на 8.4% — этого хватает</t>
         </is>
       </c>
       <c r="T18" s="14" t="inlineStr">
         <is>
-          <t>Упак Маффин шоколадный (24шт) · RP* Упак Маффин шоколадный (24шт)</t>
+          <t>RP* Упак Пирожок с картофелем готов СМ (30 шт гофра) · Упак Пирожок с картофелем готов СМ (30 шт гофра)</t>
         </is>
       </c>
     </row>
@@ -4117,31 +4117,31 @@
         </is>
       </c>
       <c r="D19" s="16" t="n">
-        <v>3374756</v>
+        <v>3331175</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>7070</v>
+        <v>7043</v>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.02718255545943404</v>
+        <v>0.01803067648812484</v>
       </c>
       <c r="H19" s="18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I19" s="17" t="n">
         <v>0.5883854469281138</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>0.4262948207171313</v>
+        <v>0.3018348623853211</v>
       </c>
       <c r="K19" s="17" t="n">
-        <v>0.04</v>
+        <v>0.055</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>0.04</v>
+        <v>0.055</v>
       </c>
       <c r="M19" s="16">
         <f>ROUND(F19*(1+L19),0)</f>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="S19" s="19" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 2.7% при ориентире 5.3%; берут на 43% больше</t>
+          <t>за 9 мес цена выросла на 1.8% при ориентире 6.0%; берут на 30% больше</t>
         </is>
       </c>
       <c r="T19" s="19" t="inlineStr">
@@ -4181,45 +4181,45 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Пирожок с капустой (30 шт гофра)</t>
+          <t>Манты с говядиной (1порц)</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Выпечка_</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>2 — следом + 2-й шаг</t>
+          <t>Горячее</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>— не трогать</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>3212485</v>
+        <v>3130667</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>756</v>
+        <v>3407</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>4251</v>
+        <v>919</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.01425098681656201</v>
+        <v>0.1717550647996697</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>0.6255704727025964</v>
+        <v>0.5940000000000001</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>0.6239255014326648</v>
+        <v>0.004717908393945258</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="M20" s="10">
         <f>ROUND(F20*(1+L20),0)</f>
@@ -4247,19 +4247,19 @@
       </c>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена упала на 1.4% при ориентире 5.3%; берут на 62% больше. Расчёт просит 8.5% — остальное вторым шагом через квартал</t>
+          <t>цену уже подняли на 17.2% — этого хватает</t>
         </is>
       </c>
       <c r="T20" s="14" t="inlineStr">
         <is>
-          <t>RP* Упак Пирожок с капустой  готов СМ (30 шт гофра) · Упак Пирожок с капустой  готов СМ (30 шт гофра)</t>
+          <t>Упак Манты с говядиной (1порц) · RP* Упак Манты с говядиной (1порц)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Манты с говядиной (1порц)</t>
+          <t>Шницель куриный с картофельным пюре (1порц)</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -4267,37 +4267,37 @@
           <t>Горячее</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>— не трогать</t>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>2 — следом</t>
         </is>
       </c>
       <c r="D21" s="16" t="n">
-        <v>2987025</v>
+        <v>3055830</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>3451</v>
+        <v>3344</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>865</v>
+        <v>914</v>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.09012158410248471</v>
+        <v>0.06280981995184831</v>
       </c>
       <c r="H21" s="18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>0.5940000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="J21" s="17" t="n">
-        <v>-0.007476993865030646</v>
+        <v>0.4621775251421076</v>
       </c>
       <c r="K21" s="17" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="M21" s="16">
         <f>ROUND(F21*(1+L21),0)</f>
@@ -4325,19 +4325,19 @@
       </c>
       <c r="S21" s="19" t="inlineStr">
         <is>
-          <t>цену уже подняли на 9.0% — этого хватает</t>
+          <t>берут на 46% больше</t>
         </is>
       </c>
       <c r="T21" s="19" t="inlineStr">
         <is>
-          <t>Упак Манты с говядиной (1порц) · RP* Упак Манты с говядиной (1порц)</t>
+          <t>Упак Шницель куриный с картофельным пюре (1порц)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Сочник творожный (30шт гофра )</t>
+          <t>Пирожок с капустой (30 шт гофра)</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -4351,31 +4351,31 @@
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>2815730</v>
+        <v>2847780</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>409</v>
+        <v>605</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>6890</v>
+        <v>4704</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01415503666138584</v>
+        <v>0.003503049327609808</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>0.6284698035678137</v>
+        <v>0.6255704727025964</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>0.5880829015544042</v>
+        <v>0.05031810294968198</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>0.08</v>
+        <v>0.055</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>0.08</v>
+        <v>0.055</v>
       </c>
       <c r="M22" s="10">
         <f>ROUND(F22*(1+L22),0)</f>
@@ -4403,57 +4403,57 @@
       </c>
       <c r="S22" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена упала на 1.4% при ориентире 5.3%; берут на 59% больше</t>
+          <t>за 9 мес цена выросла на 0.4% при ориентире 6.0%</t>
         </is>
       </c>
       <c r="T22" s="14" t="inlineStr">
         <is>
-          <t>RP* Упак Сочник творожный готов СМ (30шт гофра ) · Упак Сочник творожный готов СМ (30шт гофра )</t>
+          <t>RP* Упак Пирожок с капустой  готов СМ (30 шт гофра) · Упак Пирожок с капустой  готов СМ (30 шт гофра)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>Бризоль с рисом (1порц)</t>
+          <t>Клаб Сэндвич с курицей (1шт)</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Горячее</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>2 — следом</t>
+          <t>СЭНДВИЧИ</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>— не трогать</t>
         </is>
       </c>
       <c r="D23" s="16" t="n">
-        <v>2634834</v>
+        <v>2840700</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>2227</v>
+        <v>5463</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>1183</v>
+        <v>520</v>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.02382420203660618</v>
+        <v>0.0614001313010184</v>
       </c>
       <c r="H23" s="18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>0.374</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>0.3294866693195387</v>
+        <v>0.2881395897194059</v>
       </c>
       <c r="K23" s="17" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="M23" s="16">
         <f>ROUND(F23*(1+L23),0)</f>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="S23" s="19" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 2.4% при ориентире 5.3%; маржа 37% — тоньше заводской; берут на 33% больше</t>
+          <t>признаков отставания цены нет</t>
         </is>
       </c>
       <c r="T23" s="19" t="inlineStr">
         <is>
-          <t>Упак Бризоль с рисом (1порц)</t>
+          <t>Упак Клаб Сэндвич с курицей (1шт)</t>
         </is>
       </c>
     </row>
@@ -4507,25 +4507,25 @@
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2632371</v>
+        <v>2707461</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>2836</v>
+        <v>2852</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>928</v>
+        <v>949</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0.07048326431697016</v>
+        <v>0.1132930616573253</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I24" s="11" t="n">
         <v>0.555</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>0.06297638385605397</v>
+        <v>0.0962203715566945</v>
       </c>
       <c r="K24" s="11" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="S24" s="14" t="inlineStr">
         <is>
-          <t>признаков отставания цены нет</t>
+          <t>цену уже подняли на 11.3% — этого хватает</t>
         </is>
       </c>
       <c r="T24" s="14" t="inlineStr">
@@ -4571,45 +4571,45 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>Самса с говядиной (30 шт гофра)</t>
+          <t>Курица с сыром с пастой фузилли (1порц)</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Выпечка_</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>2 — следом + 2-й шаг</t>
+          <t>Горячее</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>— не трогать</t>
         </is>
       </c>
       <c r="D25" s="16" t="n">
-        <v>2627782</v>
+        <v>2695268</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>385</v>
+        <v>2477</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>6831</v>
+        <v>1088</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>-0.02818816478082753</v>
+        <v>0.06349256328931974</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.445</v>
+        <v>0.5740000000000001</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.7379518072289157</v>
+        <v>0.05329553508150253</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="M25" s="16">
         <f>ROUND(F25*(1+L25),0)</f>
@@ -4637,57 +4637,57 @@
       </c>
       <c r="S25" s="19" t="inlineStr">
         <is>
-          <t>за 8 мес цена упала на 2.8% при ориентире 5.3%; маржа 44% — тоньше заводской; берут на 74% больше. Расчёт просит 12.5% — остальное вторым шагом через квартал</t>
+          <t>признаков отставания цены нет</t>
         </is>
       </c>
       <c r="T25" s="19" t="inlineStr">
         <is>
-          <t>Упак Самса с говядиной готов ФЗ СМ (30 шт гофра)</t>
+          <t>Упак Курица с сыром с пастой фузилли (1порц)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Самса с курицей (30шт гофра )</t>
+          <t>Курица с сыром и гречкой (1порц)</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Выпечка_</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
-        <is>
-          <t>2 — следом + 2-й шаг</t>
+          <t>Горячее</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>— не трогать</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2612647</v>
+        <v>2687797</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>385</v>
+        <v>2531</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>6786</v>
+        <v>1062</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>-0.02307711041129701</v>
+        <v>0.1152252466027064</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.616</v>
+        <v>0.5979999999999999</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>0.6176470588235294</v>
+        <v>0.3439546822446451</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="M26" s="10">
         <f>ROUND(F26*(1+L26),0)</f>
@@ -4715,57 +4715,57 @@
       </c>
       <c r="S26" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена упала на 2.3% при ориентире 5.3%; берут на 62% больше. Расчёт просит 9.0% — остальное вторым шагом через квартал</t>
+          <t>цену уже подняли на 11.5% — этого хватает</t>
         </is>
       </c>
       <c r="T26" s="14" t="inlineStr">
         <is>
-          <t>Упак Самса с курицей готов ФЗ СМ (30шт гофра )</t>
+          <t>Упак Курица с сыром и гречкой (1порц)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>Круассан с индейкой (1шт)</t>
+          <t>Сочник творожный (30шт гофра )</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>СЭНДВИЧИ</t>
+          <t>Выпечка_</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>2 — следом</t>
+          <t>2 — следом + 2-й шаг</t>
         </is>
       </c>
       <c r="D27" s="16" t="n">
-        <v>2604922</v>
+        <v>2676020</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>4286</v>
+        <v>389</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>608</v>
+        <v>6885</v>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.03115280716362023</v>
+        <v>-0.01415503666138584</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>0.6110000000000001</v>
+        <v>0.6284698035678137</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>0.3193104863533758</v>
+        <v>0.3130630630630631</v>
       </c>
       <c r="K27" s="17" t="n">
-        <v>0.035</v>
+        <v>0.08</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>0.035</v>
+        <v>0.08</v>
       </c>
       <c r="M27" s="16">
         <f>ROUND(F27*(1+L27),0)</f>
@@ -4793,12 +4793,12 @@
       </c>
       <c r="S27" s="19" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 3.1% при ориентире 5.3%; берут на 32% больше</t>
+          <t>за 9 мес цена упала на 1.4% при ориентире 6.0%; берут на 31% больше. Расчёт просит 9.0% — остальное вторым шагом через квартал</t>
         </is>
       </c>
       <c r="T27" s="19" t="inlineStr">
         <is>
-          <t>Упак Круассан с индейкой (1шт)</t>
+          <t>Упак Сочник творожный готов СМ (30шт гофра ) · RP* Упак Сочник творожный готов СМ (30шт гофра )</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J310"/>
+  <dimension ref="A1:K310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4874,6 +4874,7 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4941,11 +4942,16 @@
           <t>авг'26</t>
         </is>
       </c>
+      <c r="K4" s="27" t="inlineStr">
+        <is>
+          <t>сен'26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="28" t="inlineStr">
         <is>
-          <t>Брецель-дог (20шт)</t>
+          <t>Сосиска в тесте (30шт гофра)</t>
         </is>
       </c>
       <c r="B5" s="29" t="inlineStr">
@@ -4954,34 +4960,37 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>10296</v>
+        <v>8795</v>
       </c>
       <c r="D5" s="30" t="n">
-        <v>7263</v>
+        <v>9210</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>7107</v>
+        <v>9434</v>
       </c>
       <c r="F5" s="30" t="n">
-        <v>7102</v>
+        <v>9473</v>
       </c>
       <c r="G5" s="30" t="n">
-        <v>7077</v>
+        <v>9406</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>7066</v>
+        <v>9349</v>
       </c>
       <c r="I5" s="30" t="n">
-        <v>7123</v>
+        <v>9358</v>
       </c>
       <c r="J5" s="30" t="n">
-        <v>7012</v>
+        <v>9393</v>
+      </c>
+      <c r="K5" s="30" t="n">
+        <v>9710</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 54%</t>
+          <t>Выпечка_ · маржа 60%</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
@@ -4990,34 +4999,37 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>170</v>
+        <v>838</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>118</v>
+        <v>628</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>563</v>
+        <v>869</v>
       </c>
       <c r="F6" s="32" t="n">
-        <v>1101</v>
+        <v>707</v>
       </c>
       <c r="G6" s="32" t="n">
-        <v>1369</v>
+        <v>714</v>
       </c>
       <c r="H6" s="32" t="n">
-        <v>1646</v>
+        <v>943</v>
       </c>
       <c r="I6" s="32" t="n">
-        <v>780</v>
+        <v>1315</v>
       </c>
       <c r="J6" s="32" t="n">
-        <v>2456</v>
+        <v>953</v>
+      </c>
+      <c r="K6" s="32" t="n">
+        <v>718</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>Сосиска в тесте (30шт гофра)</t>
+          <t>Брецель-дог (20шт)</t>
         </is>
       </c>
       <c r="B21" s="29" t="inlineStr">
@@ -5026,34 +5038,37 @@
         </is>
       </c>
       <c r="C21" s="30" t="n">
-        <v>8795</v>
+        <v>10296</v>
       </c>
       <c r="D21" s="30" t="n">
-        <v>9210</v>
+        <v>7263</v>
       </c>
       <c r="E21" s="30" t="n">
-        <v>9434</v>
+        <v>7107</v>
       </c>
       <c r="F21" s="30" t="n">
-        <v>9473</v>
+        <v>7102</v>
       </c>
       <c r="G21" s="30" t="n">
-        <v>9406</v>
+        <v>7077</v>
       </c>
       <c r="H21" s="30" t="n">
-        <v>9349</v>
+        <v>7066</v>
       </c>
       <c r="I21" s="30" t="n">
-        <v>9358</v>
+        <v>7123</v>
       </c>
       <c r="J21" s="30" t="n">
-        <v>9393</v>
+        <v>7012</v>
+      </c>
+      <c r="K21" s="30" t="n">
+        <v>7264</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 60%</t>
+          <t>Выпечка_ · маржа 54%</t>
         </is>
       </c>
       <c r="B22" s="29" t="inlineStr">
@@ -5062,28 +5077,31 @@
         </is>
       </c>
       <c r="C22" s="32" t="n">
-        <v>838</v>
+        <v>170</v>
       </c>
       <c r="D22" s="32" t="n">
-        <v>628</v>
+        <v>118</v>
       </c>
       <c r="E22" s="32" t="n">
-        <v>869</v>
+        <v>563</v>
       </c>
       <c r="F22" s="32" t="n">
-        <v>707</v>
+        <v>1101</v>
       </c>
       <c r="G22" s="32" t="n">
-        <v>714</v>
+        <v>1369</v>
       </c>
       <c r="H22" s="32" t="n">
-        <v>943</v>
+        <v>1646</v>
       </c>
       <c r="I22" s="32" t="n">
-        <v>1315</v>
+        <v>780</v>
       </c>
       <c r="J22" s="32" t="n">
-        <v>953</v>
+        <v>2456</v>
+      </c>
+      <c r="K22" s="32" t="n">
+        <v>653</v>
       </c>
     </row>
     <row r="37">
@@ -5121,6 +5139,9 @@
       <c r="J37" s="30" t="n">
         <v>891</v>
       </c>
+      <c r="K37" s="30" t="n">
+        <v>893</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="31" t="inlineStr">
@@ -5157,6 +5178,9 @@
       <c r="J38" s="32" t="n">
         <v>7265</v>
       </c>
+      <c r="K38" s="32" t="n">
+        <v>6325</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="28" t="inlineStr">
@@ -5193,6 +5217,9 @@
       <c r="J53" s="30" t="n">
         <v>1082</v>
       </c>
+      <c r="K53" s="30" t="n">
+        <v>1083</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="31" t="inlineStr">
@@ -5229,11 +5256,14 @@
       <c r="J54" s="32" t="n">
         <v>5387</v>
       </c>
+      <c r="K54" s="32" t="n">
+        <v>4824</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="28" t="inlineStr">
         <is>
-          <t>Пирожок с курицей и сыром (30 шт гофра)</t>
+          <t>Кимпаб с тунцом (1шт)</t>
         </is>
       </c>
       <c r="B69" s="29" t="inlineStr">
@@ -5242,34 +5272,37 @@
         </is>
       </c>
       <c r="C69" s="30" t="n">
-        <v>4975</v>
+        <v>855</v>
       </c>
       <c r="D69" s="30" t="n">
-        <v>5256</v>
+        <v>871</v>
       </c>
       <c r="E69" s="30" t="n">
-        <v>5348</v>
+        <v>875</v>
       </c>
       <c r="F69" s="30" t="n">
-        <v>5270</v>
+        <v>874</v>
       </c>
       <c r="G69" s="30" t="n">
-        <v>5354</v>
+        <v>879</v>
       </c>
       <c r="H69" s="30" t="n">
-        <v>5220</v>
+        <v>878</v>
       </c>
       <c r="I69" s="30" t="n">
-        <v>5294</v>
+        <v>970</v>
       </c>
       <c r="J69" s="30" t="n">
-        <v>5288</v>
+        <v>1002</v>
+      </c>
+      <c r="K69" s="30" t="n">
+        <v>979</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 50%</t>
+          <t>Япония · маржа 55%</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
@@ -5278,34 +5311,37 @@
         </is>
       </c>
       <c r="C70" s="32" t="n">
-        <v>711</v>
+        <v>4068</v>
       </c>
       <c r="D70" s="32" t="n">
-        <v>584</v>
+        <v>4158</v>
       </c>
       <c r="E70" s="32" t="n">
-        <v>791</v>
+        <v>3935</v>
       </c>
       <c r="F70" s="32" t="n">
-        <v>567</v>
+        <v>4522</v>
       </c>
       <c r="G70" s="32" t="n">
-        <v>688</v>
+        <v>4734</v>
       </c>
       <c r="H70" s="32" t="n">
-        <v>879</v>
+        <v>5532</v>
       </c>
       <c r="I70" s="32" t="n">
-        <v>1123</v>
+        <v>5257</v>
       </c>
       <c r="J70" s="32" t="n">
-        <v>937</v>
+        <v>5347</v>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>5351</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="28" t="inlineStr">
         <is>
-          <t>Кимпаб с тунцом (1шт)</t>
+          <t>Пирожок с курицей и сыром (30 шт гофра)</t>
         </is>
       </c>
       <c r="B85" s="29" t="inlineStr">
@@ -5314,34 +5350,37 @@
         </is>
       </c>
       <c r="C85" s="30" t="n">
-        <v>855</v>
+        <v>4975</v>
       </c>
       <c r="D85" s="30" t="n">
-        <v>871</v>
+        <v>5256</v>
       </c>
       <c r="E85" s="30" t="n">
-        <v>875</v>
+        <v>5348</v>
       </c>
       <c r="F85" s="30" t="n">
-        <v>874</v>
+        <v>5270</v>
       </c>
       <c r="G85" s="30" t="n">
-        <v>879</v>
+        <v>5354</v>
       </c>
       <c r="H85" s="30" t="n">
-        <v>878</v>
+        <v>5220</v>
       </c>
       <c r="I85" s="30" t="n">
-        <v>970</v>
+        <v>5294</v>
       </c>
       <c r="J85" s="30" t="n">
-        <v>1002</v>
+        <v>5288</v>
+      </c>
+      <c r="K85" s="30" t="n">
+        <v>5349</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="31" t="inlineStr">
         <is>
-          <t>Япония · маржа 55%</t>
+          <t>Выпечка_ · маржа 50%</t>
         </is>
       </c>
       <c r="B86" s="29" t="inlineStr">
@@ -5350,28 +5389,31 @@
         </is>
       </c>
       <c r="C86" s="32" t="n">
-        <v>4068</v>
+        <v>711</v>
       </c>
       <c r="D86" s="32" t="n">
-        <v>4158</v>
+        <v>584</v>
       </c>
       <c r="E86" s="32" t="n">
-        <v>3935</v>
+        <v>791</v>
       </c>
       <c r="F86" s="32" t="n">
-        <v>4522</v>
+        <v>567</v>
       </c>
       <c r="G86" s="32" t="n">
-        <v>4734</v>
+        <v>688</v>
       </c>
       <c r="H86" s="32" t="n">
-        <v>5532</v>
+        <v>879</v>
       </c>
       <c r="I86" s="32" t="n">
-        <v>5257</v>
+        <v>1123</v>
       </c>
       <c r="J86" s="32" t="n">
-        <v>5347</v>
+        <v>937</v>
+      </c>
+      <c r="K86" s="32" t="n">
+        <v>621</v>
       </c>
     </row>
     <row r="101">
@@ -5409,6 +5451,9 @@
       <c r="J101" s="30" t="n">
         <v>853</v>
       </c>
+      <c r="K101" s="30" t="n">
+        <v>838</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="31" t="inlineStr">
@@ -5445,11 +5490,14 @@
       <c r="J102" s="32" t="n">
         <v>5267</v>
       </c>
+      <c r="K102" s="32" t="n">
+        <v>5522</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="28" t="inlineStr">
         <is>
-          <t>Курица с сыром и картофельным пюре (1порц)</t>
+          <t>Маффин шоколадный (24шт)</t>
         </is>
       </c>
       <c r="B117" s="29" t="inlineStr">
@@ -5458,34 +5506,37 @@
         </is>
       </c>
       <c r="C117" s="30" t="n">
-        <v>1027</v>
+        <v>7362</v>
       </c>
       <c r="D117" s="30" t="n">
-        <v>1042</v>
+        <v>7317</v>
       </c>
       <c r="E117" s="30" t="n">
-        <v>1075</v>
+        <v>7431</v>
       </c>
       <c r="F117" s="30" t="n">
-        <v>1076</v>
+        <v>7492</v>
       </c>
       <c r="G117" s="30" t="n">
-        <v>1135</v>
+        <v>7496</v>
       </c>
       <c r="H117" s="30" t="n">
-        <v>1117</v>
+        <v>7329</v>
       </c>
       <c r="I117" s="30" t="n">
-        <v>1125</v>
+        <v>7335</v>
       </c>
       <c r="J117" s="30" t="n">
-        <v>1137</v>
+        <v>7358</v>
+      </c>
+      <c r="K117" s="30" t="n">
+        <v>7306</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 58%</t>
+          <t>Выпечка_ · маржа 49%</t>
         </is>
       </c>
       <c r="B118" s="29" t="inlineStr">
@@ -5494,34 +5545,37 @@
         </is>
       </c>
       <c r="C118" s="32" t="n">
-        <v>2525</v>
+        <v>293</v>
       </c>
       <c r="D118" s="32" t="n">
-        <v>2315</v>
+        <v>324</v>
       </c>
       <c r="E118" s="32" t="n">
-        <v>2676</v>
+        <v>387</v>
       </c>
       <c r="F118" s="32" t="n">
-        <v>2774</v>
+        <v>523</v>
       </c>
       <c r="G118" s="32" t="n">
-        <v>4267</v>
+        <v>369</v>
       </c>
       <c r="H118" s="32" t="n">
-        <v>4300</v>
+        <v>392</v>
       </c>
       <c r="I118" s="32" t="n">
-        <v>3609</v>
+        <v>456</v>
       </c>
       <c r="J118" s="32" t="n">
-        <v>3534</v>
+        <v>598</v>
+      </c>
+      <c r="K118" s="32" t="n">
+        <v>656</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="28" t="inlineStr">
         <is>
-          <t>Курица с сыром с рисом и паутини (1порц)</t>
+          <t>Курица с сыром и картофельным пюре (1порц)</t>
         </is>
       </c>
       <c r="B133" s="29" t="inlineStr">
@@ -5530,34 +5584,37 @@
         </is>
       </c>
       <c r="C133" s="30" t="n">
-        <v>1003</v>
+        <v>1027</v>
       </c>
       <c r="D133" s="30" t="n">
-        <v>1020</v>
+        <v>1042</v>
       </c>
       <c r="E133" s="30" t="n">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="F133" s="30" t="n">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="G133" s="30" t="n">
-        <v>1064</v>
+        <v>1135</v>
       </c>
       <c r="H133" s="30" t="n">
-        <v>1043</v>
+        <v>1117</v>
       </c>
       <c r="I133" s="30" t="n">
-        <v>1092</v>
+        <v>1125</v>
       </c>
       <c r="J133" s="30" t="n">
-        <v>1115</v>
+        <v>1137</v>
+      </c>
+      <c r="K133" s="30" t="n">
+        <v>1113</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 59%</t>
+          <t>Горячее · маржа 58%</t>
         </is>
       </c>
       <c r="B134" s="29" t="inlineStr">
@@ -5566,34 +5623,37 @@
         </is>
       </c>
       <c r="C134" s="32" t="n">
-        <v>2254</v>
+        <v>2525</v>
       </c>
       <c r="D134" s="32" t="n">
-        <v>2108</v>
+        <v>2315</v>
       </c>
       <c r="E134" s="32" t="n">
-        <v>2608</v>
+        <v>2676</v>
       </c>
       <c r="F134" s="32" t="n">
-        <v>3048</v>
+        <v>2774</v>
       </c>
       <c r="G134" s="32" t="n">
-        <v>3227</v>
+        <v>4267</v>
       </c>
       <c r="H134" s="32" t="n">
-        <v>3859</v>
+        <v>4300</v>
       </c>
       <c r="I134" s="32" t="n">
-        <v>3501</v>
+        <v>3609</v>
       </c>
       <c r="J134" s="32" t="n">
-        <v>3185</v>
+        <v>3534</v>
+      </c>
+      <c r="K134" s="32" t="n">
+        <v>3574</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="28" t="inlineStr">
         <is>
-          <t>Пирожок с картофелем (30 шт гофра)</t>
+          <t>Курица с сыром с рисом и паутини (1порц)</t>
         </is>
       </c>
       <c r="B149" s="29" t="inlineStr">
@@ -5602,34 +5662,37 @@
         </is>
       </c>
       <c r="C149" s="30" t="n">
-        <v>5445</v>
+        <v>1003</v>
       </c>
       <c r="D149" s="30" t="n">
-        <v>872</v>
+        <v>1020</v>
       </c>
       <c r="E149" s="30" t="n">
-        <v>4427</v>
+        <v>1071</v>
       </c>
       <c r="F149" s="30" t="n">
-        <v>4820</v>
+        <v>1074</v>
       </c>
       <c r="G149" s="30" t="n">
-        <v>4804</v>
+        <v>1064</v>
       </c>
       <c r="H149" s="30" t="n">
-        <v>4116</v>
+        <v>1043</v>
       </c>
       <c r="I149" s="30" t="n">
-        <v>4801</v>
+        <v>1092</v>
       </c>
       <c r="J149" s="30" t="n">
-        <v>4756</v>
+        <v>1115</v>
+      </c>
+      <c r="K149" s="30" t="n">
+        <v>1103</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 60%</t>
+          <t>Горячее · маржа 59%</t>
         </is>
       </c>
       <c r="B150" s="29" t="inlineStr">
@@ -5638,34 +5701,37 @@
         </is>
       </c>
       <c r="C150" s="32" t="n">
-        <v>60</v>
+        <v>2254</v>
       </c>
       <c r="D150" s="32" t="n">
-        <v>182</v>
+        <v>2108</v>
       </c>
       <c r="E150" s="32" t="n">
-        <v>550</v>
+        <v>2608</v>
       </c>
       <c r="F150" s="32" t="n">
-        <v>402</v>
+        <v>3048</v>
       </c>
       <c r="G150" s="32" t="n">
-        <v>451</v>
+        <v>3227</v>
       </c>
       <c r="H150" s="32" t="n">
-        <v>751</v>
+        <v>3859</v>
       </c>
       <c r="I150" s="32" t="n">
-        <v>971</v>
+        <v>3501</v>
       </c>
       <c r="J150" s="32" t="n">
-        <v>756</v>
+        <v>3185</v>
+      </c>
+      <c r="K150" s="32" t="n">
+        <v>3112</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="28" t="inlineStr">
         <is>
-          <t>Маффин шоколадный (24шт)</t>
+          <t>Пирожок с картофелем (30 шт гофра)</t>
         </is>
       </c>
       <c r="B165" s="29" t="inlineStr">
@@ -5674,34 +5740,37 @@
         </is>
       </c>
       <c r="C165" s="30" t="n">
-        <v>7362</v>
+        <v>5445</v>
       </c>
       <c r="D165" s="30" t="n">
-        <v>7317</v>
+        <v>872</v>
       </c>
       <c r="E165" s="30" t="n">
-        <v>7431</v>
+        <v>4427</v>
       </c>
       <c r="F165" s="30" t="n">
-        <v>7492</v>
+        <v>4820</v>
       </c>
       <c r="G165" s="30" t="n">
-        <v>7496</v>
+        <v>4804</v>
       </c>
       <c r="H165" s="30" t="n">
-        <v>7329</v>
+        <v>4116</v>
       </c>
       <c r="I165" s="30" t="n">
-        <v>7335</v>
+        <v>4801</v>
       </c>
       <c r="J165" s="30" t="n">
-        <v>7358</v>
+        <v>4756</v>
+      </c>
+      <c r="K165" s="30" t="n">
+        <v>4860</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 49%</t>
+          <t>Выпечка_ · маржа 60%</t>
         </is>
       </c>
       <c r="B166" s="29" t="inlineStr">
@@ -5710,28 +5779,31 @@
         </is>
       </c>
       <c r="C166" s="32" t="n">
-        <v>293</v>
+        <v>60</v>
       </c>
       <c r="D166" s="32" t="n">
-        <v>324</v>
+        <v>182</v>
       </c>
       <c r="E166" s="32" t="n">
-        <v>387</v>
+        <v>550</v>
       </c>
       <c r="F166" s="32" t="n">
-        <v>523</v>
+        <v>402</v>
       </c>
       <c r="G166" s="32" t="n">
-        <v>369</v>
+        <v>451</v>
       </c>
       <c r="H166" s="32" t="n">
-        <v>392</v>
+        <v>751</v>
       </c>
       <c r="I166" s="32" t="n">
-        <v>456</v>
+        <v>971</v>
       </c>
       <c r="J166" s="32" t="n">
-        <v>598</v>
+        <v>756</v>
+      </c>
+      <c r="K166" s="32" t="n">
+        <v>501</v>
       </c>
     </row>
     <row r="181">
@@ -5769,6 +5841,9 @@
       <c r="J181" s="30" t="n">
         <v>6946</v>
       </c>
+      <c r="K181" s="30" t="n">
+        <v>6911</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="31" t="inlineStr">
@@ -5805,11 +5880,14 @@
       <c r="J182" s="32" t="n">
         <v>444</v>
       </c>
+      <c r="K182" s="32" t="n">
+        <v>408</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="28" t="inlineStr">
         <is>
-          <t>Пирожок с капустой (30 шт гофра)</t>
+          <t>Манты с говядиной (1порц)</t>
         </is>
       </c>
       <c r="B197" s="29" t="inlineStr">
@@ -5818,34 +5896,37 @@
         </is>
       </c>
       <c r="C197" s="30" t="n">
-        <v>4310</v>
+        <v>831</v>
       </c>
       <c r="D197" s="30" t="n">
-        <v>4715</v>
+        <v>801</v>
       </c>
       <c r="E197" s="30" t="n">
-        <v>4746</v>
+        <v>790</v>
       </c>
       <c r="F197" s="30" t="n">
-        <v>4788</v>
+        <v>795</v>
       </c>
       <c r="G197" s="30" t="n">
-        <v>4792</v>
+        <v>848</v>
       </c>
       <c r="H197" s="30" t="n">
-        <v>3492</v>
+        <v>790</v>
       </c>
       <c r="I197" s="30" t="n">
-        <v>4647</v>
+        <v>873</v>
       </c>
       <c r="J197" s="30" t="n">
-        <v>4731</v>
+        <v>939</v>
+      </c>
+      <c r="K197" s="30" t="n">
+        <v>941</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 63%</t>
+          <t>Горячее · маржа 59%</t>
         </is>
       </c>
       <c r="B198" s="29" t="inlineStr">
@@ -5854,34 +5935,37 @@
         </is>
       </c>
       <c r="C198" s="32" t="n">
-        <v>381</v>
+        <v>3204</v>
       </c>
       <c r="D198" s="32" t="n">
-        <v>349</v>
+        <v>3017</v>
       </c>
       <c r="E198" s="32" t="n">
-        <v>496</v>
+        <v>3925</v>
       </c>
       <c r="F198" s="32" t="n">
-        <v>446</v>
+        <v>3334</v>
       </c>
       <c r="G198" s="32" t="n">
-        <v>454</v>
+        <v>3173</v>
       </c>
       <c r="H198" s="32" t="n">
-        <v>829</v>
+        <v>3667</v>
       </c>
       <c r="I198" s="32" t="n">
-        <v>724</v>
+        <v>3234</v>
       </c>
       <c r="J198" s="32" t="n">
-        <v>714</v>
+        <v>3453</v>
+      </c>
+      <c r="K198" s="32" t="n">
+        <v>3535</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="28" t="inlineStr">
         <is>
-          <t>Манты с говядиной (1порц)</t>
+          <t>Шницель куриный с картофельным пюре (1порц)</t>
         </is>
       </c>
       <c r="B213" s="29" t="inlineStr">
@@ -5890,34 +5974,37 @@
         </is>
       </c>
       <c r="C213" s="30" t="n">
-        <v>831</v>
+        <v>859</v>
       </c>
       <c r="D213" s="30" t="n">
-        <v>801</v>
+        <v>841</v>
       </c>
       <c r="E213" s="30" t="n">
-        <v>790</v>
+        <v>857</v>
       </c>
       <c r="F213" s="30" t="n">
-        <v>795</v>
+        <v>856</v>
       </c>
       <c r="G213" s="30" t="n">
-        <v>848</v>
+        <v>899</v>
       </c>
       <c r="H213" s="30" t="n">
-        <v>790</v>
+        <v>812</v>
       </c>
       <c r="I213" s="30" t="n">
-        <v>873</v>
+        <v>891</v>
       </c>
       <c r="J213" s="30" t="n">
-        <v>939</v>
+        <v>911</v>
+      </c>
+      <c r="K213" s="30" t="n">
+        <v>932</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 59%</t>
+          <t>Горячее · маржа 55%</t>
         </is>
       </c>
       <c r="B214" s="29" t="inlineStr">
@@ -5926,34 +6013,37 @@
         </is>
       </c>
       <c r="C214" s="32" t="n">
-        <v>3204</v>
+        <v>2443</v>
       </c>
       <c r="D214" s="32" t="n">
-        <v>3017</v>
+        <v>2194</v>
       </c>
       <c r="E214" s="32" t="n">
-        <v>3925</v>
+        <v>1988</v>
       </c>
       <c r="F214" s="32" t="n">
-        <v>3334</v>
+        <v>2128</v>
       </c>
       <c r="G214" s="32" t="n">
-        <v>3173</v>
+        <v>2114</v>
       </c>
       <c r="H214" s="32" t="n">
-        <v>3667</v>
+        <v>2619</v>
       </c>
       <c r="I214" s="32" t="n">
-        <v>3234</v>
+        <v>2763</v>
       </c>
       <c r="J214" s="32" t="n">
-        <v>3453</v>
+        <v>3372</v>
+      </c>
+      <c r="K214" s="32" t="n">
+        <v>3897</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="28" t="inlineStr">
         <is>
-          <t>Сочник творожный (30шт гофра )</t>
+          <t>Пирожок с капустой (30 шт гофра)</t>
         </is>
       </c>
       <c r="B229" s="29" t="inlineStr">
@@ -5962,28 +6052,31 @@
         </is>
       </c>
       <c r="C229" s="30" t="n">
-        <v>7012</v>
+        <v>4310</v>
       </c>
       <c r="D229" s="30" t="n">
-        <v>6983</v>
+        <v>4715</v>
       </c>
       <c r="E229" s="30" t="n">
-        <v>7182</v>
+        <v>4746</v>
       </c>
       <c r="F229" s="30" t="n">
-        <v>7137</v>
+        <v>4788</v>
       </c>
       <c r="G229" s="30" t="n">
-        <v>7249</v>
+        <v>4792</v>
       </c>
       <c r="H229" s="30" t="n">
-        <v>6963</v>
+        <v>3492</v>
       </c>
       <c r="I229" s="30" t="n">
-        <v>6912</v>
+        <v>4647</v>
       </c>
       <c r="J229" s="30" t="n">
-        <v>6814</v>
+        <v>4731</v>
+      </c>
+      <c r="K229" s="30" t="n">
+        <v>4763</v>
       </c>
     </row>
     <row r="230">
@@ -5998,34 +6091,37 @@
         </is>
       </c>
       <c r="C230" s="32" t="n">
-        <v>210</v>
+        <v>381</v>
       </c>
       <c r="D230" s="32" t="n">
-        <v>169</v>
+        <v>349</v>
       </c>
       <c r="E230" s="32" t="n">
-        <v>231</v>
+        <v>496</v>
       </c>
       <c r="F230" s="32" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
       <c r="G230" s="32" t="n">
-        <v>235</v>
+        <v>454</v>
       </c>
       <c r="H230" s="32" t="n">
-        <v>347</v>
+        <v>829</v>
       </c>
       <c r="I230" s="32" t="n">
-        <v>418</v>
+        <v>724</v>
       </c>
       <c r="J230" s="32" t="n">
-        <v>461</v>
+        <v>714</v>
+      </c>
+      <c r="K230" s="32" t="n">
+        <v>378</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="28" t="inlineStr">
         <is>
-          <t>Бризоль с рисом (1порц)</t>
+          <t>Клаб Сэндвич с курицей (1шт)</t>
         </is>
       </c>
       <c r="B245" s="29" t="inlineStr">
@@ -6034,34 +6130,37 @@
         </is>
       </c>
       <c r="C245" s="30" t="n">
-        <v>1149</v>
+        <v>488</v>
       </c>
       <c r="D245" s="30" t="n">
-        <v>1154</v>
+        <v>489</v>
       </c>
       <c r="E245" s="30" t="n">
-        <v>1226</v>
+        <v>512</v>
       </c>
       <c r="F245" s="30" t="n">
-        <v>1202</v>
+        <v>506</v>
       </c>
       <c r="G245" s="30" t="n">
-        <v>1207</v>
+        <v>509</v>
       </c>
       <c r="H245" s="30" t="n">
-        <v>1188</v>
+        <v>514</v>
       </c>
       <c r="I245" s="30" t="n">
-        <v>1179</v>
+        <v>516</v>
       </c>
       <c r="J245" s="30" t="n">
-        <v>1182</v>
+        <v>524</v>
+      </c>
+      <c r="K245" s="30" t="n">
+        <v>519</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 37%</t>
+          <t>СЭНДВИЧИ · маржа 57%</t>
         </is>
       </c>
       <c r="B246" s="29" t="inlineStr">
@@ -6070,28 +6169,31 @@
         </is>
       </c>
       <c r="C246" s="32" t="n">
-        <v>1835</v>
+        <v>3237</v>
       </c>
       <c r="D246" s="32" t="n">
-        <v>1583</v>
+        <v>3273</v>
       </c>
       <c r="E246" s="32" t="n">
-        <v>1421</v>
+        <v>4099</v>
       </c>
       <c r="F246" s="32" t="n">
-        <v>1789</v>
+        <v>4262</v>
       </c>
       <c r="G246" s="32" t="n">
-        <v>1816</v>
+        <v>4270</v>
       </c>
       <c r="H246" s="32" t="n">
-        <v>2234</v>
+        <v>4191</v>
       </c>
       <c r="I246" s="32" t="n">
-        <v>2204</v>
+        <v>5051</v>
       </c>
       <c r="J246" s="32" t="n">
-        <v>2244</v>
+        <v>5713</v>
+      </c>
+      <c r="K246" s="32" t="n">
+        <v>5625</v>
       </c>
     </row>
     <row r="261">
@@ -6129,6 +6231,9 @@
       <c r="J261" s="30" t="n">
         <v>961</v>
       </c>
+      <c r="K261" s="30" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="31" t="inlineStr">
@@ -6165,11 +6270,14 @@
       <c r="J262" s="32" t="n">
         <v>2945</v>
       </c>
+      <c r="K262" s="32" t="n">
+        <v>2779</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="28" t="inlineStr">
         <is>
-          <t>Самса с говядиной (30 шт гофра)</t>
+          <t>Курица с сыром с пастой фузилли (1порц)</t>
         </is>
       </c>
       <c r="B277" s="29" t="inlineStr">
@@ -6178,34 +6286,37 @@
         </is>
       </c>
       <c r="C277" s="30" t="n">
-        <v>7098</v>
+        <v>1032</v>
       </c>
       <c r="D277" s="30" t="n">
-        <v>6977</v>
+        <v>1031</v>
       </c>
       <c r="E277" s="30" t="n">
-        <v>7003</v>
+        <v>1074</v>
       </c>
       <c r="F277" s="30" t="n">
-        <v>6964</v>
+        <v>1048</v>
       </c>
       <c r="G277" s="30" t="n">
-        <v>6862</v>
+        <v>1066</v>
       </c>
       <c r="H277" s="30" t="n">
-        <v>6912</v>
+        <v>1006</v>
       </c>
       <c r="I277" s="30" t="n">
-        <v>6774</v>
+        <v>1065</v>
       </c>
       <c r="J277" s="30" t="n">
-        <v>6805</v>
+        <v>1097</v>
+      </c>
+      <c r="K277" s="30" t="n">
+        <v>1099</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 44%</t>
+          <t>Горячее · маржа 57%</t>
         </is>
       </c>
       <c r="B278" s="29" t="inlineStr">
@@ -6214,34 +6325,37 @@
         </is>
       </c>
       <c r="C278" s="32" t="n">
-        <v>186</v>
+        <v>2109</v>
       </c>
       <c r="D278" s="32" t="n">
-        <v>130</v>
+        <v>1993</v>
       </c>
       <c r="E278" s="32" t="n">
-        <v>217</v>
+        <v>2249</v>
       </c>
       <c r="F278" s="32" t="n">
-        <v>210</v>
+        <v>2438</v>
       </c>
       <c r="G278" s="32" t="n">
-        <v>237</v>
+        <v>2252</v>
       </c>
       <c r="H278" s="32" t="n">
-        <v>357</v>
+        <v>2365</v>
       </c>
       <c r="I278" s="32" t="n">
-        <v>256</v>
+        <v>2244</v>
       </c>
       <c r="J278" s="32" t="n">
-        <v>541</v>
+        <v>2571</v>
+      </c>
+      <c r="K278" s="32" t="n">
+        <v>2616</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="28" t="inlineStr">
         <is>
-          <t>Самса с курицей (30шт гофра )</t>
+          <t>Курица с сыром и гречкой (1порц)</t>
         </is>
       </c>
       <c r="B293" s="29" t="inlineStr">
@@ -6250,34 +6364,37 @@
         </is>
       </c>
       <c r="C293" s="30" t="n">
-        <v>6935</v>
+        <v>943</v>
       </c>
       <c r="D293" s="30" t="n">
-        <v>6925</v>
+        <v>958</v>
       </c>
       <c r="E293" s="30" t="n">
-        <v>6901</v>
+        <v>973</v>
       </c>
       <c r="F293" s="30" t="n">
-        <v>6983</v>
+        <v>977</v>
       </c>
       <c r="G293" s="30" t="n">
-        <v>6703</v>
+        <v>1003</v>
       </c>
       <c r="H293" s="30" t="n">
-        <v>6897</v>
+        <v>928</v>
       </c>
       <c r="I293" s="30" t="n">
-        <v>6710</v>
+        <v>1032</v>
       </c>
       <c r="J293" s="30" t="n">
-        <v>6765</v>
+        <v>1082</v>
+      </c>
+      <c r="K293" s="30" t="n">
+        <v>1068</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 62%</t>
+          <t>Горячее · маржа 60%</t>
         </is>
       </c>
       <c r="B294" s="29" t="inlineStr">
@@ -6286,34 +6403,37 @@
         </is>
       </c>
       <c r="C294" s="32" t="n">
-        <v>218</v>
+        <v>1542</v>
       </c>
       <c r="D294" s="32" t="n">
-        <v>161</v>
+        <v>1552</v>
       </c>
       <c r="E294" s="32" t="n">
-        <v>211</v>
+        <v>1506</v>
       </c>
       <c r="F294" s="32" t="n">
-        <v>253</v>
+        <v>1743</v>
       </c>
       <c r="G294" s="32" t="n">
-        <v>250</v>
+        <v>1690</v>
       </c>
       <c r="H294" s="32" t="n">
-        <v>301</v>
+        <v>2216</v>
       </c>
       <c r="I294" s="32" t="n">
-        <v>285</v>
+        <v>2266</v>
       </c>
       <c r="J294" s="32" t="n">
-        <v>569</v>
+        <v>2484</v>
+      </c>
+      <c r="K294" s="32" t="n">
+        <v>2842</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="28" t="inlineStr">
         <is>
-          <t>Круассан с индейкой (1шт)</t>
+          <t>Сочник творожный (30шт гофра )</t>
         </is>
       </c>
       <c r="B309" s="29" t="inlineStr">
@@ -6322,34 +6442,37 @@
         </is>
       </c>
       <c r="C309" s="30" t="n">
-        <v>590</v>
+        <v>7012</v>
       </c>
       <c r="D309" s="30" t="n">
-        <v>599</v>
+        <v>6983</v>
       </c>
       <c r="E309" s="30" t="n">
-        <v>593</v>
+        <v>7182</v>
       </c>
       <c r="F309" s="30" t="n">
-        <v>577</v>
+        <v>7137</v>
       </c>
       <c r="G309" s="30" t="n">
-        <v>587</v>
+        <v>7249</v>
       </c>
       <c r="H309" s="30" t="n">
-        <v>595</v>
+        <v>6963</v>
       </c>
       <c r="I309" s="30" t="n">
-        <v>611</v>
+        <v>6912</v>
       </c>
       <c r="J309" s="30" t="n">
-        <v>619</v>
+        <v>6814</v>
+      </c>
+      <c r="K309" s="30" t="n">
+        <v>6959</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="31" t="inlineStr">
         <is>
-          <t>СЭНДВИЧИ · маржа 61%</t>
+          <t>Выпечка_ · маржа 63%</t>
         </is>
       </c>
       <c r="B310" s="29" t="inlineStr">
@@ -6358,28 +6481,31 @@
         </is>
       </c>
       <c r="C310" s="32" t="n">
-        <v>2352</v>
+        <v>210</v>
       </c>
       <c r="D310" s="32" t="n">
-        <v>2345</v>
+        <v>169</v>
       </c>
       <c r="E310" s="32" t="n">
-        <v>2472</v>
+        <v>231</v>
       </c>
       <c r="F310" s="32" t="n">
-        <v>3314</v>
+        <v>306</v>
       </c>
       <c r="G310" s="32" t="n">
-        <v>3960</v>
+        <v>235</v>
       </c>
       <c r="H310" s="32" t="n">
-        <v>4761</v>
+        <v>347</v>
       </c>
       <c r="I310" s="32" t="n">
-        <v>4156</v>
+        <v>418</v>
       </c>
       <c r="J310" s="32" t="n">
-        <v>3941</v>
+        <v>461</v>
+      </c>
+      <c r="K310" s="32" t="n">
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -6410,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 30.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 01.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3274,7 +3274,7 @@
         <v>9</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.5969786552575863</v>
+        <v>0.6064702261650977</v>
       </c>
       <c r="J8" s="11" t="n">
         <v>0.2631133671742809</v>
@@ -3352,7 +3352,7 @@
         <v>7</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.53968</v>
+        <v>0.5606472719661988</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>-0.05515063168124401</v>
@@ -3415,10 +3415,10 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>6031604</v>
+        <v>6029346</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>6799</v>
+        <v>6797</v>
       </c>
       <c r="F10" s="10" t="n">
         <v>887</v>
@@ -3430,10 +3430,10 @@
         <v>9</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>0.543</v>
+        <v>0.5110000000000001</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>0.05628916161773079</v>
+        <v>0.05592667391642059</v>
       </c>
       <c r="K10" s="11" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>9</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>0.476</v>
+        <v>0.484</v>
       </c>
       <c r="J11" s="17" t="n">
         <v>-0.002570694087403624</v>
@@ -3571,25 +3571,25 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>5232716</v>
+        <v>5231855</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>5318</v>
+        <v>5317</v>
       </c>
       <c r="F12" s="10" t="n">
         <v>984</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.12493049455731</v>
+        <v>0.1250068184951663</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.546</v>
+        <v>0.551</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>0.07891533675953477</v>
+        <v>0.07871246956992151</v>
       </c>
       <c r="K12" s="11" t="n">
         <v>0</v>
@@ -3664,7 +3664,7 @@
         <v>9</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>0.4993299298854</v>
+        <v>0.5103551421387045</v>
       </c>
       <c r="J13" s="17" t="n">
         <v>0.2563261480787253</v>
@@ -3727,25 +3727,25 @@
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>4461715</v>
+        <v>4460795</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>5326</v>
+        <v>5325</v>
       </c>
       <c r="F14" s="10" t="n">
         <v>838</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.1164652186153825</v>
+        <v>0.1164064477289919</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.498</v>
+        <v>0.506</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>0.01331895731591293</v>
+        <v>0.01312868649711429</v>
       </c>
       <c r="K14" s="11" t="n">
         <v>0</v>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="D15" s="16" t="n">
-        <v>4179161</v>
+        <v>4174489</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F15" s="16" t="n">
         <v>7332</v>
@@ -3820,10 +3820,10 @@
         <v>9</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.4937349562821021</v>
+        <v>0.4888987037775798</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>0.3317757009345794</v>
+        <v>0.3302180685358256</v>
       </c>
       <c r="K15" s="17" t="n">
         <v>0.08</v>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>4018098</v>
+        <v>4017657</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>3572</v>
@@ -3898,10 +3898,10 @@
         <v>9</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>0.583</v>
+        <v>0.593</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>-0.05502160303324222</v>
+        <v>-0.05510977867912892</v>
       </c>
       <c r="K16" s="11" t="n">
         <v>0</v>
@@ -3976,7 +3976,7 @@
         <v>9</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>0.589</v>
+        <v>0.598</v>
       </c>
       <c r="J17" s="17" t="n">
         <v>-0.03315571343990531</v>
@@ -4054,7 +4054,7 @@
         <v>8</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>0.6046347372539482</v>
+        <v>0.6398560004713844</v>
       </c>
       <c r="J18" s="11" t="n">
         <v>0.3890274314214464</v>
@@ -4132,7 +4132,7 @@
         <v>9</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>0.5883854469281138</v>
+        <v>0.5905305045547496</v>
       </c>
       <c r="J19" s="17" t="n">
         <v>0.3018348623853211</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>3130667</v>
+        <v>3130296</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>3407</v>
@@ -4213,7 +4213,7 @@
         <v>0.5940000000000001</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>0.004717908393945258</v>
+        <v>0.004619618635738121</v>
       </c>
       <c r="K20" s="11" t="n">
         <v>0</v>
@@ -4288,7 +4288,7 @@
         <v>9</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>0.554</v>
+        <v>0.575</v>
       </c>
       <c r="J21" s="17" t="n">
         <v>0.4621775251421076</v>
@@ -4366,7 +4366,7 @@
         <v>9</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>0.6255704727025964</v>
+        <v>0.6632496049554389</v>
       </c>
       <c r="J22" s="11" t="n">
         <v>0.05031810294968198</v>
@@ -4429,25 +4429,25 @@
         </is>
       </c>
       <c r="D23" s="16" t="n">
-        <v>2840700</v>
+        <v>2839947</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>5463</v>
+        <v>5462</v>
       </c>
       <c r="F23" s="16" t="n">
         <v>520</v>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.0614001313010184</v>
+        <v>0.061334318036534</v>
       </c>
       <c r="H23" s="18" t="n">
         <v>9</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>0.2881395897194059</v>
+        <v>0.2878251984594828</v>
       </c>
       <c r="K23" s="17" t="n">
         <v>0</v>
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2707461</v>
+        <v>2706691</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="F24" s="10" t="n">
         <v>949</v>
@@ -4522,10 +4522,10 @@
         <v>9</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>0.555</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>0.0962203715566945</v>
+        <v>0.09583600256246004</v>
       </c>
       <c r="K24" s="11" t="n">
         <v>0</v>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="D25" s="16" t="n">
-        <v>2695268</v>
+        <v>2693504</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="F25" s="16" t="n">
         <v>1088</v>
@@ -4600,10 +4600,10 @@
         <v>9</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.5740000000000001</v>
+        <v>0.583</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.05329553508150253</v>
+        <v>0.0527285613040398</v>
       </c>
       <c r="K25" s="17" t="n">
         <v>0</v>
@@ -4663,25 +4663,25 @@
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2687797</v>
+        <v>2687470</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="F26" s="10" t="n">
         <v>1062</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.1152252466027064</v>
+        <v>0.1152577075384189</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.5979999999999999</v>
+        <v>0.606</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>0.3439546822446451</v>
+        <v>0.34377765976279</v>
       </c>
       <c r="K26" s="11" t="n">
         <v>0</v>
@@ -4756,7 +4756,7 @@
         <v>9</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>0.6284698035678137</v>
+        <v>0.6428580615989417</v>
       </c>
       <c r="J27" s="17" t="n">
         <v>0.3130630630630631</v>
@@ -4990,7 +4990,7 @@
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 60%</t>
+          <t>Выпечка_ · маржа 61%</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
@@ -5068,7 +5068,7 @@
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 54%</t>
+          <t>Выпечка_ · маржа 56%</t>
         </is>
       </c>
       <c r="B22" s="29" t="inlineStr">
@@ -5140,13 +5140,13 @@
         <v>891</v>
       </c>
       <c r="K37" s="30" t="n">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 54%</t>
+          <t>Горячее · маржа 51%</t>
         </is>
       </c>
       <c r="B38" s="29" t="inlineStr">
@@ -5179,7 +5179,7 @@
         <v>7265</v>
       </c>
       <c r="K38" s="32" t="n">
-        <v>6325</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="53">
@@ -5296,7 +5296,7 @@
         <v>1002</v>
       </c>
       <c r="K69" s="30" t="n">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="70">
@@ -5335,7 +5335,7 @@
         <v>5347</v>
       </c>
       <c r="K70" s="32" t="n">
-        <v>5351</v>
+        <v>5348</v>
       </c>
     </row>
     <row r="85">
@@ -5380,7 +5380,7 @@
     <row r="86">
       <c r="A86" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 50%</t>
+          <t>Выпечка_ · маржа 51%</t>
         </is>
       </c>
       <c r="B86" s="29" t="inlineStr">
@@ -5458,7 +5458,7 @@
     <row r="102">
       <c r="A102" s="31" t="inlineStr">
         <is>
-          <t>Япония · маржа 50%</t>
+          <t>Япония · маржа 51%</t>
         </is>
       </c>
       <c r="B102" s="29" t="inlineStr">
@@ -5491,7 +5491,7 @@
         <v>5267</v>
       </c>
       <c r="K102" s="32" t="n">
-        <v>5522</v>
+        <v>5519</v>
       </c>
     </row>
     <row r="117">
@@ -5530,7 +5530,7 @@
         <v>7358</v>
       </c>
       <c r="K117" s="30" t="n">
-        <v>7306</v>
+        <v>7307</v>
       </c>
     </row>
     <row r="118">
@@ -5569,7 +5569,7 @@
         <v>598</v>
       </c>
       <c r="K118" s="32" t="n">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="133">
@@ -5614,7 +5614,7 @@
     <row r="134">
       <c r="A134" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 58%</t>
+          <t>Горячее · маржа 59%</t>
         </is>
       </c>
       <c r="B134" s="29" t="inlineStr">
@@ -5647,7 +5647,7 @@
         <v>3534</v>
       </c>
       <c r="K134" s="32" t="n">
-        <v>3574</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="149">
@@ -5692,7 +5692,7 @@
     <row r="150">
       <c r="A150" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 59%</t>
+          <t>Горячее · маржа 60%</t>
         </is>
       </c>
       <c r="B150" s="29" t="inlineStr">
@@ -5770,7 +5770,7 @@
     <row r="166">
       <c r="A166" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 60%</t>
+          <t>Выпечка_ · маржа 64%</t>
         </is>
       </c>
       <c r="B166" s="29" t="inlineStr">
@@ -5959,7 +5959,7 @@
         <v>3453</v>
       </c>
       <c r="K198" s="32" t="n">
-        <v>3535</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="213">
@@ -6004,7 +6004,7 @@
     <row r="214">
       <c r="A214" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 55%</t>
+          <t>Горячее · маржа 57%</t>
         </is>
       </c>
       <c r="B214" s="29" t="inlineStr">
@@ -6082,7 +6082,7 @@
     <row r="230">
       <c r="A230" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 63%</t>
+          <t>Выпечка_ · маржа 66%</t>
         </is>
       </c>
       <c r="B230" s="29" t="inlineStr">
@@ -6160,7 +6160,7 @@
     <row r="246">
       <c r="A246" s="31" t="inlineStr">
         <is>
-          <t>СЭНДВИЧИ · маржа 57%</t>
+          <t>СЭНДВИЧИ · маржа 56%</t>
         </is>
       </c>
       <c r="B246" s="29" t="inlineStr">
@@ -6193,7 +6193,7 @@
         <v>5713</v>
       </c>
       <c r="K246" s="32" t="n">
-        <v>5625</v>
+        <v>5621</v>
       </c>
     </row>
     <row r="261">
@@ -6232,7 +6232,7 @@
         <v>961</v>
       </c>
       <c r="K261" s="30" t="n">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="262">
@@ -6271,7 +6271,7 @@
         <v>2945</v>
       </c>
       <c r="K262" s="32" t="n">
-        <v>2779</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="277">
@@ -6316,7 +6316,7 @@
     <row r="278">
       <c r="A278" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 57%</t>
+          <t>Горячее · маржа 58%</t>
         </is>
       </c>
       <c r="B278" s="29" t="inlineStr">
@@ -6349,7 +6349,7 @@
         <v>2571</v>
       </c>
       <c r="K278" s="32" t="n">
-        <v>2616</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="293">
@@ -6394,7 +6394,7 @@
     <row r="294">
       <c r="A294" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 60%</t>
+          <t>Горячее · маржа 61%</t>
         </is>
       </c>
       <c r="B294" s="29" t="inlineStr">
@@ -6427,7 +6427,7 @@
         <v>2484</v>
       </c>
       <c r="K294" s="32" t="n">
-        <v>2842</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="309">
@@ -6472,7 +6472,7 @@
     <row r="310">
       <c r="A310" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 63%</t>
+          <t>Выпечка_ · маржа 64%</t>
         </is>
       </c>
       <c r="B310" s="29" t="inlineStr">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3415,10 +3415,10 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>6029346</v>
+        <v>6027604</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>6797</v>
+        <v>6795</v>
       </c>
       <c r="F10" s="10" t="n">
         <v>887</v>
@@ -3430,10 +3430,10 @@
         <v>9</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>0.5110000000000001</v>
+        <v>0.511</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>0.05592667391642059</v>
+        <v>0.05566775412977054</v>
       </c>
       <c r="K10" s="11" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>4017657</v>
+        <v>4017216</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>3572</v>
@@ -3901,7 +3901,7 @@
         <v>0.593</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>-0.05510977867912892</v>
+        <v>-0.05519795432501551</v>
       </c>
       <c r="K16" s="11" t="n">
         <v>0</v>
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="D17" s="16" t="n">
-        <v>3602692</v>
+        <v>3602251</v>
       </c>
       <c r="E17" s="16" t="n">
         <v>3266</v>
@@ -3970,7 +3970,7 @@
         <v>1103</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.08149746441462312</v>
+        <v>0.08142816931867337</v>
       </c>
       <c r="H17" s="18" t="n">
         <v>9</v>
@@ -3979,7 +3979,7 @@
         <v>0.598</v>
       </c>
       <c r="J17" s="17" t="n">
-        <v>-0.03315571343990531</v>
+        <v>-0.0332543911584765</v>
       </c>
       <c r="K17" s="17" t="n">
         <v>0</v>
@@ -4429,16 +4429,16 @@
         </is>
       </c>
       <c r="D23" s="16" t="n">
-        <v>2839947</v>
+        <v>2839745</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>5462</v>
+        <v>5461</v>
       </c>
       <c r="F23" s="16" t="n">
         <v>520</v>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.061334318036534</v>
+        <v>0.06130358056301843</v>
       </c>
       <c r="H23" s="18" t="n">
         <v>9</v>
@@ -4447,7 +4447,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>0.2878251984594828</v>
+        <v>0.287746600644502</v>
       </c>
       <c r="K23" s="17" t="n">
         <v>0</v>
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2706691</v>
+        <v>2701842</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>2851</v>
+        <v>2846</v>
       </c>
       <c r="F24" s="10" t="n">
         <v>949</v>
@@ -4525,7 +4525,7 @@
         <v>0.5620000000000001</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>0.09583600256246004</v>
+        <v>0.09404228058936592</v>
       </c>
       <c r="K24" s="11" t="n">
         <v>0</v>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="D25" s="16" t="n">
-        <v>2693504</v>
+        <v>2693063</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="F25" s="16" t="n">
         <v>1088</v>
@@ -4603,7 +4603,7 @@
         <v>0.583</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.0527285613040398</v>
+        <v>0.05258681785967423</v>
       </c>
       <c r="K25" s="17" t="n">
         <v>0</v>
@@ -5179,7 +5179,7 @@
         <v>7265</v>
       </c>
       <c r="K38" s="32" t="n">
-        <v>6318</v>
+        <v>6313</v>
       </c>
     </row>
     <row r="53">
@@ -5647,7 +5647,7 @@
         <v>3534</v>
       </c>
       <c r="K134" s="32" t="n">
-        <v>3573</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="149">
@@ -5725,7 +5725,7 @@
         <v>3185</v>
       </c>
       <c r="K150" s="32" t="n">
-        <v>3112</v>
+        <v>3111</v>
       </c>
     </row>
     <row r="165">
@@ -6193,7 +6193,7 @@
         <v>5713</v>
       </c>
       <c r="K246" s="32" t="n">
-        <v>5621</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="261">
@@ -6232,7 +6232,7 @@
         <v>961</v>
       </c>
       <c r="K261" s="30" t="n">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="262">
@@ -6271,7 +6271,7 @@
         <v>2945</v>
       </c>
       <c r="K262" s="32" t="n">
-        <v>2776</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="277">
@@ -6349,7 +6349,7 @@
         <v>2571</v>
       </c>
       <c r="K278" s="32" t="n">
-        <v>2612</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="293">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 01.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 02.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 01.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 02.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3337,13 +3337,13 @@
         </is>
       </c>
       <c r="D9" s="16" t="n">
-        <v>9173640</v>
+        <v>9170667</v>
       </c>
       <c r="E9" s="16" t="n">
         <v>1296</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>7077</v>
+        <v>7076</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>0.00286179319379154</v>
@@ -3352,10 +3352,10 @@
         <v>7</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.5606472719661988</v>
+        <v>0.5606455364931666</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>-0.05515063168124401</v>
+        <v>-0.05539358600583089</v>
       </c>
       <c r="K9" s="17" t="n">
         <v>0.045</v>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>5231855</v>
+        <v>5231467</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>5317</v>
@@ -3580,7 +3580,7 @@
         <v>984</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.1250068184951663</v>
+        <v>0.1249676252689662</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>9</v>
@@ -3589,7 +3589,7 @@
         <v>0.551</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>0.07871246956992151</v>
+        <v>0.07864484717338383</v>
       </c>
       <c r="K12" s="11" t="n">
         <v>0</v>
@@ -3727,16 +3727,16 @@
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>4460795</v>
+        <v>4460125</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>5325</v>
+        <v>5324</v>
       </c>
       <c r="F14" s="10" t="n">
         <v>838</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.1164064477289919</v>
+        <v>0.1163253817025949</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>9</v>
@@ -3745,7 +3745,7 @@
         <v>0.506</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>0.01312868649711429</v>
+        <v>0.01300183928458165</v>
       </c>
       <c r="K14" s="11" t="n">
         <v>0</v>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="D17" s="16" t="n">
-        <v>3602251</v>
+        <v>3601271</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>3266</v>
+        <v>3265</v>
       </c>
       <c r="F17" s="16" t="n">
         <v>1103</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.08142816931867337</v>
+        <v>0.08154460970238953</v>
       </c>
       <c r="H17" s="18" t="n">
         <v>9</v>
@@ -3979,7 +3979,7 @@
         <v>0.598</v>
       </c>
       <c r="J17" s="17" t="n">
-        <v>-0.0332543911584765</v>
+        <v>-0.03355042431418986</v>
       </c>
       <c r="K17" s="17" t="n">
         <v>0</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>3130296</v>
+        <v>3130022</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>3407</v>
@@ -4213,7 +4213,7 @@
         <v>0.5940000000000001</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>0.004619618635738121</v>
+        <v>0.004521328877530761</v>
       </c>
       <c r="K20" s="11" t="n">
         <v>0</v>
@@ -5062,7 +5062,7 @@
         <v>7012</v>
       </c>
       <c r="K21" s="30" t="n">
-        <v>7264</v>
+        <v>7261</v>
       </c>
     </row>
     <row r="22">
@@ -5101,7 +5101,7 @@
         <v>2456</v>
       </c>
       <c r="K22" s="32" t="n">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="37">
@@ -5296,7 +5296,7 @@
         <v>1002</v>
       </c>
       <c r="K69" s="30" t="n">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="70">
@@ -5335,7 +5335,7 @@
         <v>5347</v>
       </c>
       <c r="K70" s="32" t="n">
-        <v>5348</v>
+        <v>5347</v>
       </c>
     </row>
     <row r="85">
@@ -5491,7 +5491,7 @@
         <v>5267</v>
       </c>
       <c r="K102" s="32" t="n">
-        <v>5519</v>
+        <v>5517</v>
       </c>
     </row>
     <row r="117">
@@ -5725,7 +5725,7 @@
         <v>3185</v>
       </c>
       <c r="K150" s="32" t="n">
-        <v>3111</v>
+        <v>3108</v>
       </c>
     </row>
     <row r="165">
@@ -5959,7 +5959,7 @@
         <v>3453</v>
       </c>
       <c r="K198" s="32" t="n">
-        <v>3534</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="213">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3415,10 +3415,10 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>6027604</v>
+        <v>6024469</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>6795</v>
+        <v>6792</v>
       </c>
       <c r="F10" s="10" t="n">
         <v>887</v>
@@ -3433,7 +3433,7 @@
         <v>0.511</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>0.05566775412977054</v>
+        <v>0.05520169851380041</v>
       </c>
       <c r="K10" s="11" t="n">
         <v>0</v>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D11" s="16" t="n">
-        <v>5428360</v>
+        <v>5427078</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>5044</v>
+        <v>5043</v>
       </c>
       <c r="F11" s="16" t="n">
         <v>1076</v>
@@ -3511,7 +3511,7 @@
         <v>0.484</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>-0.002570694087403624</v>
+        <v>-0.002768439786434596</v>
       </c>
       <c r="K11" s="17" t="n">
         <v>0</v>
@@ -3571,16 +3571,16 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>5231467</v>
+        <v>5228756</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>5317</v>
+        <v>5315</v>
       </c>
       <c r="F12" s="10" t="n">
         <v>984</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.1249676252689662</v>
+        <v>0.1246928616704577</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>9</v>
@@ -3589,7 +3589,7 @@
         <v>0.551</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>0.07864484717338383</v>
+        <v>0.07817149039761984</v>
       </c>
       <c r="K12" s="11" t="n">
         <v>0</v>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>4460125</v>
+        <v>4459789</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>5324</v>
@@ -3736,7 +3736,7 @@
         <v>838</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.1163253817025949</v>
+        <v>0.1162848266446101</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>9</v>
@@ -3745,7 +3745,7 @@
         <v>0.506</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>0.01300183928458165</v>
+        <v>0.01293841567831544</v>
       </c>
       <c r="K14" s="11" t="n">
         <v>0</v>
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>4017216</v>
+        <v>4016334</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>3572</v>
+        <v>3571</v>
       </c>
       <c r="F16" s="10" t="n">
         <v>1125</v>
@@ -3898,10 +3898,10 @@
         <v>9</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>0.593</v>
+        <v>0.5930000000000001</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>-0.05519795432501551</v>
+        <v>-0.0553743056167887</v>
       </c>
       <c r="K16" s="11" t="n">
         <v>0</v>
@@ -3961,25 +3961,25 @@
         </is>
       </c>
       <c r="D17" s="16" t="n">
-        <v>3601271</v>
+        <v>3600389</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="F17" s="16" t="n">
         <v>1103</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.08154460970238953</v>
+        <v>0.08140582676728837</v>
       </c>
       <c r="H17" s="18" t="n">
         <v>9</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>0.598</v>
+        <v>0.5980000000000001</v>
       </c>
       <c r="J17" s="17" t="n">
-        <v>-0.03355042431418986</v>
+        <v>-0.03374777975133214</v>
       </c>
       <c r="K17" s="17" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>3130022</v>
+        <v>3128538</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>3407</v>
+        <v>3405</v>
       </c>
       <c r="F20" s="10" t="n">
         <v>919</v>
@@ -4210,10 +4210,10 @@
         <v>9</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>0.5940000000000001</v>
+        <v>0.594</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>0.004521328877530761</v>
+        <v>0.004128169844702212</v>
       </c>
       <c r="K20" s="11" t="n">
         <v>0</v>
@@ -4429,16 +4429,16 @@
         </is>
       </c>
       <c r="D23" s="16" t="n">
-        <v>2839745</v>
+        <v>2838336</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>5461</v>
+        <v>5459</v>
       </c>
       <c r="F23" s="16" t="n">
         <v>520</v>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.06130358056301843</v>
+        <v>0.06108811158556904</v>
       </c>
       <c r="H23" s="18" t="n">
         <v>9</v>
@@ -4447,7 +4447,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>0.287746600644502</v>
+        <v>0.287196415939637</v>
       </c>
       <c r="K23" s="17" t="n">
         <v>0</v>
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2701842</v>
+        <v>2697686</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>2846</v>
+        <v>2842</v>
       </c>
       <c r="F24" s="10" t="n">
         <v>949</v>
@@ -4522,10 +4522,10 @@
         <v>9</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5609999999999999</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>0.09404228058936592</v>
+        <v>0.09250480461242816</v>
       </c>
       <c r="K24" s="11" t="n">
         <v>0</v>
@@ -5179,7 +5179,7 @@
         <v>7265</v>
       </c>
       <c r="K38" s="32" t="n">
-        <v>6313</v>
+        <v>6304</v>
       </c>
     </row>
     <row r="53">
@@ -5257,7 +5257,7 @@
         <v>5387</v>
       </c>
       <c r="K54" s="32" t="n">
-        <v>4824</v>
+        <v>4821</v>
       </c>
     </row>
     <row r="69">
@@ -5335,7 +5335,7 @@
         <v>5347</v>
       </c>
       <c r="K70" s="32" t="n">
-        <v>5347</v>
+        <v>5340</v>
       </c>
     </row>
     <row r="85">
@@ -5491,7 +5491,7 @@
         <v>5267</v>
       </c>
       <c r="K102" s="32" t="n">
-        <v>5517</v>
+        <v>5516</v>
       </c>
     </row>
     <row r="117">
@@ -5647,7 +5647,7 @@
         <v>3534</v>
       </c>
       <c r="K134" s="32" t="n">
-        <v>3572</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="149">
@@ -5725,7 +5725,7 @@
         <v>3185</v>
       </c>
       <c r="K150" s="32" t="n">
-        <v>3108</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="165">
@@ -5959,7 +5959,7 @@
         <v>3453</v>
       </c>
       <c r="K198" s="32" t="n">
-        <v>3533</v>
+        <v>3529</v>
       </c>
     </row>
     <row r="213">
@@ -6193,7 +6193,7 @@
         <v>5713</v>
       </c>
       <c r="K246" s="32" t="n">
-        <v>5620</v>
+        <v>5613</v>
       </c>
     </row>
     <row r="261">
@@ -6271,7 +6271,7 @@
         <v>2945</v>
       </c>
       <c r="K262" s="32" t="n">
-        <v>2762</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="277">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 02.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 03.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 02.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 03.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 03.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 04.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 03.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 04.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3352,7 +3352,7 @@
         <v>7</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.5606455364931666</v>
+        <v>0.5598182611224193</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>-0.05539358600583089</v>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 04.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 05.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
         <v>9</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>0.5103551421387045</v>
+        <v>0.5080261705664453</v>
       </c>
       <c r="J13" s="17" t="n">
         <v>0.2563261480787253</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>3128538</v>
+        <v>3128263</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>3405</v>
@@ -4213,7 +4213,7 @@
         <v>0.594</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>0.004128169844702212</v>
+        <v>0.004029880086494853</v>
       </c>
       <c r="K20" s="11" t="n">
         <v>0</v>
@@ -5959,7 +5959,7 @@
         <v>3453</v>
       </c>
       <c r="K198" s="32" t="n">
-        <v>3529</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="213">
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 04.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 05.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3274,7 +3274,7 @@
         <v>9</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.6064702261650977</v>
+        <v>0.6213709800487569</v>
       </c>
       <c r="J8" s="11" t="n">
         <v>0.2631133671742809</v>
@@ -3352,7 +3352,7 @@
         <v>7</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.5598182611224193</v>
+        <v>0.5573364350101774</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>-0.05539358600583089</v>
@@ -3571,25 +3571,25 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>5228756</v>
+        <v>5227594</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>5315</v>
+        <v>5314</v>
       </c>
       <c r="F12" s="10" t="n">
         <v>984</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.1246928616704577</v>
+        <v>0.1245748852020385</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.551</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>0.07817149039761984</v>
+        <v>0.07796862320800657</v>
       </c>
       <c r="K12" s="11" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
         <v>9</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.506</v>
+        <v>0.505</v>
       </c>
       <c r="J14" s="11" t="n">
         <v>0.01293841567831544</v>
@@ -3820,7 +3820,7 @@
         <v>9</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.4888987037775798</v>
+        <v>0.4865676354185598</v>
       </c>
       <c r="J15" s="17" t="n">
         <v>0.3302180685358256</v>
@@ -3898,7 +3898,7 @@
         <v>9</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>0.5930000000000001</v>
+        <v>0.591</v>
       </c>
       <c r="J16" s="11" t="n">
         <v>-0.0553743056167887</v>
@@ -4288,7 +4288,7 @@
         <v>9</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>0.575</v>
+        <v>0.573</v>
       </c>
       <c r="J21" s="17" t="n">
         <v>0.4621775251421076</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="D23" s="16" t="n">
-        <v>2838336</v>
+        <v>2838135</v>
       </c>
       <c r="E23" s="16" t="n">
         <v>5459</v>
@@ -4438,7 +4438,7 @@
         <v>520</v>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.06108811158556904</v>
+        <v>0.06105728642384234</v>
       </c>
       <c r="H23" s="18" t="n">
         <v>9</v>
@@ -4447,7 +4447,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>0.287196415939637</v>
+        <v>0.2871178181246563</v>
       </c>
       <c r="K23" s="17" t="n">
         <v>0</v>
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="D27" s="16" t="n">
-        <v>2676020</v>
+        <v>2670260</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>6885</v>
+        <v>6882</v>
       </c>
       <c r="G27" s="17" t="n">
         <v>-0.01415503666138584</v>
@@ -4756,10 +4756,10 @@
         <v>9</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>0.6428580615989417</v>
+        <v>0.6428318703047643</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>0.3130630630630631</v>
+        <v>0.3108108108108107</v>
       </c>
       <c r="K27" s="17" t="n">
         <v>0.08</v>
@@ -4990,7 +4990,7 @@
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 61%</t>
+          <t>Выпечка_ · маржа 62%</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
@@ -5335,7 +5335,7 @@
         <v>5347</v>
       </c>
       <c r="K70" s="32" t="n">
-        <v>5340</v>
+        <v>5337</v>
       </c>
     </row>
     <row r="85">
@@ -5458,7 +5458,7 @@
     <row r="102">
       <c r="A102" s="31" t="inlineStr">
         <is>
-          <t>Япония · маржа 51%</t>
+          <t>Япония · маржа 50%</t>
         </is>
       </c>
       <c r="B102" s="29" t="inlineStr">
@@ -6193,7 +6193,7 @@
         <v>5713</v>
       </c>
       <c r="K246" s="32" t="n">
-        <v>5613</v>
+        <v>5612</v>
       </c>
     </row>
     <row r="261">
@@ -6466,7 +6466,7 @@
         <v>6814</v>
       </c>
       <c r="K309" s="30" t="n">
-        <v>6959</v>
+        <v>6947</v>
       </c>
     </row>
     <row r="310">
@@ -6505,7 +6505,7 @@
         <v>461</v>
       </c>
       <c r="K310" s="32" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 05.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 06.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
         <v>9</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.5499999999999999</v>
+        <v>0.551</v>
       </c>
       <c r="J12" s="11" t="n">
         <v>0.07796862320800657</v>
@@ -3898,7 +3898,7 @@
         <v>9</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>0.591</v>
+        <v>0.589</v>
       </c>
       <c r="J16" s="11" t="n">
         <v>-0.0553743056167887</v>
@@ -3976,7 +3976,7 @@
         <v>9</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>0.5980000000000001</v>
+        <v>0.5960000000000001</v>
       </c>
       <c r="J17" s="17" t="n">
         <v>-0.03374777975133214</v>
@@ -4288,7 +4288,7 @@
         <v>9</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>0.573</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="J21" s="17" t="n">
         <v>0.4621775251421076</v>
@@ -4600,7 +4600,7 @@
         <v>9</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.583</v>
+        <v>0.581</v>
       </c>
       <c r="J25" s="17" t="n">
         <v>0.05258681785967423</v>
@@ -4678,7 +4678,7 @@
         <v>9</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.606</v>
+        <v>0.604</v>
       </c>
       <c r="J26" s="11" t="n">
         <v>0.34377765976279</v>
@@ -6394,7 +6394,7 @@
     <row r="294">
       <c r="A294" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 61%</t>
+          <t>Горячее · маржа 60%</t>
         </is>
       </c>
       <c r="B294" s="29" t="inlineStr">
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 05.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 06.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3274,7 +3274,7 @@
         <v>9</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.6213709800487569</v>
+        <v>0.6124305277185615</v>
       </c>
       <c r="J8" s="11" t="n">
         <v>0.2631133671742809</v>
@@ -3352,7 +3352,7 @@
         <v>7</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.5573364350101774</v>
+        <v>0.5407545798197151</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>-0.05539358600583089</v>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="D15" s="16" t="n">
-        <v>4174489</v>
+        <v>4176889</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F15" s="16" t="n">
         <v>7332</v>
@@ -3820,10 +3820,10 @@
         <v>9</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.4865676354185598</v>
+        <v>0.4865655854899356</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>0.3302180685358256</v>
+        <v>0.3309968847352025</v>
       </c>
       <c r="K15" s="17" t="n">
         <v>0.08</v>
@@ -3898,7 +3898,7 @@
         <v>9</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>0.589</v>
+        <v>0.591</v>
       </c>
       <c r="J16" s="11" t="n">
         <v>-0.0553743056167887</v>
@@ -4117,13 +4117,13 @@
         </is>
       </c>
       <c r="D19" s="16" t="n">
-        <v>3331175</v>
+        <v>3332675</v>
       </c>
       <c r="E19" s="16" t="n">
         <v>473</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>7043</v>
+        <v>7041</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>0.01803067648812484</v>
@@ -4132,10 +4132,10 @@
         <v>9</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>0.5905305045547496</v>
+        <v>0.5905302657805181</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>0.3018348623853211</v>
+        <v>0.3027522935779816</v>
       </c>
       <c r="K19" s="17" t="n">
         <v>0.055</v>
@@ -4288,7 +4288,7 @@
         <v>9</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>0.5700000000000001</v>
+        <v>0.5720000000000001</v>
       </c>
       <c r="J21" s="17" t="n">
         <v>0.4621775251421076</v>
@@ -4990,7 +4990,7 @@
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 62%</t>
+          <t>Выпечка_ · маржа 61%</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
@@ -5068,7 +5068,7 @@
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 56%</t>
+          <t>Выпечка_ · маржа 54%</t>
         </is>
       </c>
       <c r="B22" s="29" t="inlineStr">
@@ -5569,7 +5569,7 @@
         <v>598</v>
       </c>
       <c r="K118" s="32" t="n">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="133">
@@ -5842,7 +5842,7 @@
         <v>6946</v>
       </c>
       <c r="K181" s="30" t="n">
-        <v>6911</v>
+        <v>6905</v>
       </c>
     </row>
     <row r="182">
@@ -5881,7 +5881,7 @@
         <v>444</v>
       </c>
       <c r="K182" s="32" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="197">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3274,7 +3274,7 @@
         <v>9</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.6124305277185615</v>
+        <v>0.6104437605340736</v>
       </c>
       <c r="J8" s="11" t="n">
         <v>0.2631133671742809</v>
@@ -3352,7 +3352,7 @@
         <v>7</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.5407545798197151</v>
+        <v>0.5399273044489677</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>-0.05539358600583089</v>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 06.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 07.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 06.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 07.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3805,13 +3805,13 @@
         </is>
       </c>
       <c r="D15" s="16" t="n">
-        <v>4176889</v>
+        <v>4179227</v>
       </c>
       <c r="E15" s="16" t="n">
         <v>570</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>7332</v>
+        <v>7328</v>
       </c>
       <c r="G15" s="17" t="n">
         <v>-0.003665392881112228</v>
@@ -3820,10 +3820,10 @@
         <v>9</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.4865655854899356</v>
+        <v>0.4857863158096235</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>0.3309968847352025</v>
+        <v>0.3325545171339566</v>
       </c>
       <c r="K15" s="17" t="n">
         <v>0.08</v>
@@ -4117,13 +4117,13 @@
         </is>
       </c>
       <c r="D19" s="16" t="n">
-        <v>3332675</v>
+        <v>3333929</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>7041</v>
+        <v>7034</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>0.01803067648812484</v>
@@ -4132,10 +4132,10 @@
         <v>9</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>0.5905302657805181</v>
+        <v>0.590530066224159</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>0.3027522935779816</v>
+        <v>0.3045871559633029</v>
       </c>
       <c r="K19" s="17" t="n">
         <v>0.055</v>
@@ -4522,7 +4522,7 @@
         <v>9</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>0.5609999999999999</v>
+        <v>0.5619999999999999</v>
       </c>
       <c r="J24" s="11" t="n">
         <v>0.09250480461242816</v>
@@ -5530,7 +5530,7 @@
         <v>7358</v>
       </c>
       <c r="K117" s="30" t="n">
-        <v>7307</v>
+        <v>7295</v>
       </c>
     </row>
     <row r="118">
@@ -5569,7 +5569,7 @@
         <v>598</v>
       </c>
       <c r="K118" s="32" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="133">
@@ -5842,7 +5842,7 @@
         <v>6946</v>
       </c>
       <c r="K181" s="30" t="n">
-        <v>6905</v>
+        <v>6881</v>
       </c>
     </row>
     <row r="182">
@@ -5881,7 +5881,7 @@
         <v>444</v>
       </c>
       <c r="K182" s="32" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="197">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 07.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 08.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
         <v>9</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.551</v>
+        <v>0.544</v>
       </c>
       <c r="J12" s="11" t="n">
         <v>0.07796862320800657</v>
@@ -3742,7 +3742,7 @@
         <v>9</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.505</v>
+        <v>0.4970000000000001</v>
       </c>
       <c r="J14" s="11" t="n">
         <v>0.01293841567831544</v>
@@ -4444,7 +4444,7 @@
         <v>9</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5589999999999999</v>
       </c>
       <c r="J23" s="17" t="n">
         <v>0.2871178181246563</v>
@@ -5302,7 +5302,7 @@
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Япония · маржа 55%</t>
+          <t>Япония · маржа 54%</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 07.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 08.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -1340,7 +1340,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Курица с сыром и гречкой (1порц)</a:t>
+              <a:t>Сочник творожный (30шт гофра )</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1542,7 +1542,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Сочник творожный (30шт гофра )</a:t>
+              <a:t>Курица с сыром и гречкой (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3274,7 +3274,7 @@
         <v>9</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.6104437605340736</v>
+        <v>0.6069669179612197</v>
       </c>
       <c r="J8" s="11" t="n">
         <v>0.2631133671742809</v>
@@ -3352,7 +3352,7 @@
         <v>7</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.5399273044489677</v>
+        <v>0.5299636522244838</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>-0.05539358600583089</v>
@@ -3586,7 +3586,7 @@
         <v>9</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.544</v>
+        <v>0.5479999999999999</v>
       </c>
       <c r="J12" s="11" t="n">
         <v>0.07796862320800657</v>
@@ -3742,7 +3742,7 @@
         <v>9</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.4970000000000001</v>
+        <v>0.502</v>
       </c>
       <c r="J14" s="11" t="n">
         <v>0.01293841567831544</v>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="D15" s="16" t="n">
-        <v>4179227</v>
+        <v>4196475</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="F15" s="16" t="n">
         <v>7328</v>
@@ -3820,10 +3820,10 @@
         <v>9</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.4857863158096235</v>
+        <v>0.485770753610332</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>0.3325545171339566</v>
+        <v>0.338006230529595</v>
       </c>
       <c r="K15" s="17" t="n">
         <v>0.08</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="S15" s="19" t="inlineStr">
         <is>
-          <t>за 9 мес цена упала на 0.4% при ориентире 6.0%; берут на 33% больше</t>
+          <t>за 9 мес цена упала на 0.4% при ориентире 6.0%; берут на 34% больше</t>
         </is>
       </c>
       <c r="T15" s="19" t="inlineStr">
@@ -3898,7 +3898,7 @@
         <v>9</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>0.591</v>
+        <v>0.592</v>
       </c>
       <c r="J16" s="11" t="n">
         <v>-0.0553743056167887</v>
@@ -3976,7 +3976,7 @@
         <v>9</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>0.5960000000000001</v>
+        <v>0.597</v>
       </c>
       <c r="J17" s="17" t="n">
         <v>-0.03374777975133214</v>
@@ -4117,13 +4117,13 @@
         </is>
       </c>
       <c r="D19" s="16" t="n">
-        <v>3333929</v>
+        <v>3348489</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>7034</v>
+        <v>7035</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>0.01803067648812484</v>
@@ -4132,10 +4132,10 @@
         <v>9</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>0.590530066224159</v>
+        <v>0.5905277613745821</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>0.3045871559633029</v>
+        <v>0.310091743119266</v>
       </c>
       <c r="K19" s="17" t="n">
         <v>0.055</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="S19" s="19" t="inlineStr">
         <is>
-          <t>за 9 мес цена выросла на 1.8% при ориентире 6.0%; берут на 30% больше</t>
+          <t>за 9 мес цена выросла на 1.8% при ориентире 6.0%; берут на 31% больше</t>
         </is>
       </c>
       <c r="T19" s="19" t="inlineStr">
@@ -4288,7 +4288,7 @@
         <v>9</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.573</v>
       </c>
       <c r="J21" s="17" t="n">
         <v>0.4621775251421076</v>
@@ -4600,7 +4600,7 @@
         <v>9</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.581</v>
+        <v>0.582</v>
       </c>
       <c r="J25" s="17" t="n">
         <v>0.05258681785967423</v>
@@ -4649,45 +4649,45 @@
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Курица с сыром и гречкой (1порц)</t>
+          <t>Сочник творожный (30шт гофра )</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Горячее</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>— не трогать</t>
+          <t>Выпечка_</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>2 — следом + 2-й шаг</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2687470</v>
+        <v>2692760</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>2530</v>
+        <v>391</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>1062</v>
+        <v>6881</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.1152577075384189</v>
+        <v>-0.01415503666138584</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.604</v>
+        <v>0.6429335440217472</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>0.34377765976279</v>
+        <v>0.322072072072072</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="M26" s="10">
         <f>ROUND(F26*(1+L26),0)</f>
@@ -4715,57 +4715,57 @@
       </c>
       <c r="S26" s="14" t="inlineStr">
         <is>
-          <t>цену уже подняли на 11.5% — этого хватает</t>
+          <t>за 9 мес цена упала на 1.4% при ориентире 6.0%; берут на 32% больше. Расчёт просит 9.0% — остальное вторым шагом через квартал</t>
         </is>
       </c>
       <c r="T26" s="14" t="inlineStr">
         <is>
-          <t>Упак Курица с сыром и гречкой (1порц)</t>
+          <t>Упак Сочник творожный готов СМ (30шт гофра ) · RP* Упак Сочник творожный готов СМ (30шт гофра )</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>Сочник творожный (30шт гофра )</t>
+          <t>Курица с сыром и гречкой (1порц)</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Выпечка_</t>
-        </is>
-      </c>
-      <c r="C27" s="21" t="inlineStr">
-        <is>
-          <t>2 — следом + 2-й шаг</t>
+          <t>Горячее</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>— не трогать</t>
         </is>
       </c>
       <c r="D27" s="16" t="n">
-        <v>2670260</v>
+        <v>2687470</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>388</v>
+        <v>2530</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>6882</v>
+        <v>1062</v>
       </c>
       <c r="G27" s="17" t="n">
-        <v>-0.01415503666138584</v>
+        <v>0.1152577075384189</v>
       </c>
       <c r="H27" s="18" t="n">
         <v>9</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>0.6428318703047643</v>
+        <v>0.605</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>0.3108108108108107</v>
+        <v>0.34377765976279</v>
       </c>
       <c r="K27" s="17" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="M27" s="16">
         <f>ROUND(F27*(1+L27),0)</f>
@@ -4793,12 +4793,12 @@
       </c>
       <c r="S27" s="19" t="inlineStr">
         <is>
-          <t>за 9 мес цена упала на 1.4% при ориентире 6.0%; берут на 31% больше. Расчёт просит 9.0% — остальное вторым шагом через квартал</t>
+          <t>цену уже подняли на 11.5% — этого хватает</t>
         </is>
       </c>
       <c r="T27" s="19" t="inlineStr">
         <is>
-          <t>Упак Сочник творожный готов СМ (30шт гофра ) · RP* Упак Сочник творожный готов СМ (30шт гофра )</t>
+          <t>Упак Курица с сыром и гречкой (1порц)</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 54%</t>
+          <t>Выпечка_ · маржа 53%</t>
         </is>
       </c>
       <c r="B22" s="29" t="inlineStr">
@@ -5302,7 +5302,7 @@
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Япония · маржа 54%</t>
+          <t>Япония · маржа 55%</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
@@ -5530,7 +5530,7 @@
         <v>7358</v>
       </c>
       <c r="K117" s="30" t="n">
-        <v>7295</v>
+        <v>7297</v>
       </c>
     </row>
     <row r="118">
@@ -5569,7 +5569,7 @@
         <v>598</v>
       </c>
       <c r="K118" s="32" t="n">
-        <v>657</v>
+        <v>664</v>
       </c>
     </row>
     <row r="133">
@@ -5842,7 +5842,7 @@
         <v>6946</v>
       </c>
       <c r="K181" s="30" t="n">
-        <v>6881</v>
+        <v>6887</v>
       </c>
     </row>
     <row r="182">
@@ -5881,7 +5881,7 @@
         <v>444</v>
       </c>
       <c r="K182" s="32" t="n">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="197">
@@ -6355,7 +6355,7 @@
     <row r="293">
       <c r="A293" s="28" t="inlineStr">
         <is>
-          <t>Курица с сыром и гречкой (1порц)</t>
+          <t>Сочник творожный (30шт гофра )</t>
         </is>
       </c>
       <c r="B293" s="29" t="inlineStr">
@@ -6364,37 +6364,37 @@
         </is>
       </c>
       <c r="C293" s="30" t="n">
-        <v>943</v>
+        <v>7012</v>
       </c>
       <c r="D293" s="30" t="n">
-        <v>958</v>
+        <v>6983</v>
       </c>
       <c r="E293" s="30" t="n">
-        <v>973</v>
+        <v>7182</v>
       </c>
       <c r="F293" s="30" t="n">
-        <v>977</v>
+        <v>7137</v>
       </c>
       <c r="G293" s="30" t="n">
-        <v>1003</v>
+        <v>7249</v>
       </c>
       <c r="H293" s="30" t="n">
-        <v>928</v>
+        <v>6963</v>
       </c>
       <c r="I293" s="30" t="n">
-        <v>1032</v>
+        <v>6912</v>
       </c>
       <c r="J293" s="30" t="n">
-        <v>1082</v>
+        <v>6814</v>
       </c>
       <c r="K293" s="30" t="n">
-        <v>1068</v>
+        <v>6940</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 60%</t>
+          <t>Выпечка_ · маржа 64%</t>
         </is>
       </c>
       <c r="B294" s="29" t="inlineStr">
@@ -6403,37 +6403,37 @@
         </is>
       </c>
       <c r="C294" s="32" t="n">
-        <v>1542</v>
+        <v>210</v>
       </c>
       <c r="D294" s="32" t="n">
-        <v>1552</v>
+        <v>169</v>
       </c>
       <c r="E294" s="32" t="n">
-        <v>1506</v>
+        <v>231</v>
       </c>
       <c r="F294" s="32" t="n">
-        <v>1743</v>
+        <v>306</v>
       </c>
       <c r="G294" s="32" t="n">
-        <v>1690</v>
+        <v>235</v>
       </c>
       <c r="H294" s="32" t="n">
-        <v>2216</v>
+        <v>347</v>
       </c>
       <c r="I294" s="32" t="n">
-        <v>2266</v>
+        <v>418</v>
       </c>
       <c r="J294" s="32" t="n">
-        <v>2484</v>
+        <v>461</v>
       </c>
       <c r="K294" s="32" t="n">
-        <v>2841</v>
+        <v>295</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="28" t="inlineStr">
         <is>
-          <t>Сочник творожный (30шт гофра )</t>
+          <t>Курица с сыром и гречкой (1порц)</t>
         </is>
       </c>
       <c r="B309" s="29" t="inlineStr">
@@ -6442,37 +6442,37 @@
         </is>
       </c>
       <c r="C309" s="30" t="n">
-        <v>7012</v>
+        <v>943</v>
       </c>
       <c r="D309" s="30" t="n">
-        <v>6983</v>
+        <v>958</v>
       </c>
       <c r="E309" s="30" t="n">
-        <v>7182</v>
+        <v>973</v>
       </c>
       <c r="F309" s="30" t="n">
-        <v>7137</v>
+        <v>977</v>
       </c>
       <c r="G309" s="30" t="n">
-        <v>7249</v>
+        <v>1003</v>
       </c>
       <c r="H309" s="30" t="n">
-        <v>6963</v>
+        <v>928</v>
       </c>
       <c r="I309" s="30" t="n">
-        <v>6912</v>
+        <v>1032</v>
       </c>
       <c r="J309" s="30" t="n">
-        <v>6814</v>
+        <v>1082</v>
       </c>
       <c r="K309" s="30" t="n">
-        <v>6947</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 64%</t>
+          <t>Горячее · маржа 60%</t>
         </is>
       </c>
       <c r="B310" s="29" t="inlineStr">
@@ -6481,31 +6481,31 @@
         </is>
       </c>
       <c r="C310" s="32" t="n">
-        <v>210</v>
+        <v>1542</v>
       </c>
       <c r="D310" s="32" t="n">
-        <v>169</v>
+        <v>1552</v>
       </c>
       <c r="E310" s="32" t="n">
-        <v>231</v>
+        <v>1506</v>
       </c>
       <c r="F310" s="32" t="n">
-        <v>306</v>
+        <v>1743</v>
       </c>
       <c r="G310" s="32" t="n">
-        <v>235</v>
+        <v>1690</v>
       </c>
       <c r="H310" s="32" t="n">
-        <v>347</v>
+        <v>2216</v>
       </c>
       <c r="I310" s="32" t="n">
-        <v>418</v>
+        <v>2266</v>
       </c>
       <c r="J310" s="32" t="n">
-        <v>461</v>
+        <v>2484</v>
       </c>
       <c r="K310" s="32" t="n">
-        <v>285</v>
+        <v>2841</v>
       </c>
     </row>
   </sheetData>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 08.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 09.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
         <v>7</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.5299636522244838</v>
+        <v>0.5291363768537366</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>-0.05539358600583089</v>
@@ -3586,7 +3586,7 @@
         <v>9</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.5479999999999999</v>
+        <v>0.547</v>
       </c>
       <c r="J12" s="11" t="n">
         <v>0.07796862320800657</v>
@@ -3664,7 +3664,7 @@
         <v>9</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>0.5080261705664453</v>
+        <v>0.5074919648808971</v>
       </c>
       <c r="J13" s="17" t="n">
         <v>0.2563261480787253</v>
@@ -3742,7 +3742,7 @@
         <v>9</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.502</v>
+        <v>0.503</v>
       </c>
       <c r="J14" s="11" t="n">
         <v>0.01293841567831544</v>
@@ -3820,7 +3820,7 @@
         <v>9</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.485770753610332</v>
+        <v>0.484770753610332</v>
       </c>
       <c r="J15" s="17" t="n">
         <v>0.338006230529595</v>
@@ -4054,7 +4054,7 @@
         <v>8</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>0.6398560004713844</v>
+        <v>0.6394539263798517</v>
       </c>
       <c r="J18" s="11" t="n">
         <v>0.3890274314214464</v>
@@ -4132,7 +4132,7 @@
         <v>9</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>0.5905277613745821</v>
+        <v>0.5900555227491641</v>
       </c>
       <c r="J19" s="17" t="n">
         <v>0.310091743119266</v>
@@ -4366,7 +4366,7 @@
         <v>9</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>0.6632496049554389</v>
+        <v>0.6622496049554392</v>
       </c>
       <c r="J22" s="11" t="n">
         <v>0.05031810294968198</v>
@@ -4678,7 +4678,7 @@
         <v>9</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.6429335440217472</v>
+        <v>0.6423804497987196</v>
       </c>
       <c r="J26" s="11" t="n">
         <v>0.322072072072072</v>
@@ -5536,7 +5536,7 @@
     <row r="118">
       <c r="A118" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 49%</t>
+          <t>Выпечка_ · маржа 48%</t>
         </is>
       </c>
       <c r="B118" s="29" t="inlineStr">
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 08.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 09.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 09.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 10.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 09.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 10.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 10.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 11.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 10.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 11.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 11.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 12.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 11.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 12.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 12.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 13.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 12.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 13.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3259,13 +3259,13 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>9409940</v>
+        <v>9407770</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>995</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>9454</v>
+        <v>9452</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>0.01983196557667033</v>
@@ -3274,7 +3274,7 @@
         <v>9</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.6069669179612197</v>
+        <v>0.6069657570284988</v>
       </c>
       <c r="J8" s="11" t="n">
         <v>0.2631133671742809</v>
@@ -4984,7 +4984,7 @@
         <v>9393</v>
       </c>
       <c r="K5" s="30" t="n">
-        <v>9710</v>
+        <v>9701</v>
       </c>
     </row>
     <row r="6">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 13.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 14.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>9407770</v>
+        <v>9407910</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>995</v>
@@ -3274,7 +3274,7 @@
         <v>9</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.6069657570284988</v>
+        <v>0.6069658319435453</v>
       </c>
       <c r="J8" s="11" t="n">
         <v>0.2631133671742809</v>
@@ -4117,13 +4117,13 @@
         </is>
       </c>
       <c r="D19" s="16" t="n">
-        <v>3348489</v>
+        <v>3348939</v>
       </c>
       <c r="E19" s="16" t="n">
         <v>476</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>7035</v>
+        <v>7036</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>0.01803067648812484</v>
@@ -4132,7 +4132,7 @@
         <v>9</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>0.5900555227491641</v>
+        <v>0.5900553809176199</v>
       </c>
       <c r="J19" s="17" t="n">
         <v>0.310091743119266</v>
@@ -4663,13 +4663,13 @@
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2692760</v>
+        <v>2691936</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>391</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>6881</v>
+        <v>6879</v>
       </c>
       <c r="G26" s="11" t="n">
         <v>-0.01415503666138584</v>
@@ -4678,7 +4678,7 @@
         <v>9</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.6423804497987196</v>
+        <v>0.6423768930613507</v>
       </c>
       <c r="J26" s="11" t="n">
         <v>0.322072072072072</v>
@@ -4984,7 +4984,7 @@
         <v>9393</v>
       </c>
       <c r="K5" s="30" t="n">
-        <v>9701</v>
+        <v>9702</v>
       </c>
     </row>
     <row r="6">
@@ -5842,7 +5842,7 @@
         <v>6946</v>
       </c>
       <c r="K181" s="30" t="n">
-        <v>6887</v>
+        <v>6890</v>
       </c>
     </row>
     <row r="182">
@@ -6388,7 +6388,7 @@
         <v>6814</v>
       </c>
       <c r="K293" s="30" t="n">
-        <v>6940</v>
+        <v>6932</v>
       </c>
     </row>
     <row r="294">
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 13.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 14.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3259,25 +3259,25 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>9407910</v>
+        <v>9399970</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>995</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>9452</v>
+        <v>9450</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.01983196557667033</v>
+        <v>0.0192572601683545</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.6069658319435453</v>
+        <v>0.6069615796646161</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>0.2631133671742809</v>
+        <v>0.2622673434856175</v>
       </c>
       <c r="K8" s="11" t="n">
         <v>0.04</v>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="S8" s="14" t="inlineStr">
         <is>
-          <t>за 9 мес цена выросла на 2.0% при ориентире 6.0%</t>
+          <t>за 9 мес цена выросла на 1.9% при ориентире 6.0%</t>
         </is>
       </c>
       <c r="T8" s="14" t="inlineStr">
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="D15" s="16" t="n">
-        <v>4196475</v>
+        <v>4194139</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F15" s="16" t="n">
         <v>7328</v>
@@ -3820,10 +3820,10 @@
         <v>9</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.484770753610332</v>
+        <v>0.4847728537985073</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>0.338006230529595</v>
+        <v>0.3372274143302181</v>
       </c>
       <c r="K15" s="17" t="n">
         <v>0.08</v>
@@ -4981,7 +4981,7 @@
         <v>9358</v>
       </c>
       <c r="J5" s="30" t="n">
-        <v>9393</v>
+        <v>9388</v>
       </c>
       <c r="K5" s="30" t="n">
         <v>9702</v>
@@ -5020,7 +5020,7 @@
         <v>1315</v>
       </c>
       <c r="J6" s="32" t="n">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="K6" s="32" t="n">
         <v>718</v>
@@ -5569,7 +5569,7 @@
         <v>598</v>
       </c>
       <c r="K118" s="32" t="n">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="133">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 14.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 15.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 14.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 15.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -4210,7 +4210,7 @@
         <v>9</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>0.594</v>
+        <v>0.598</v>
       </c>
       <c r="J20" s="11" t="n">
         <v>0.004029880086494853</v>
@@ -5926,7 +5926,7 @@
     <row r="198">
       <c r="A198" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 59%</t>
+          <t>Горячее · маржа 60%</t>
         </is>
       </c>
       <c r="B198" s="29" t="inlineStr">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 15.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 16.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 15.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 16.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 16.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 17.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 16.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 17.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 17.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 18.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 17.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 18.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 18.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 19.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 18.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 19.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 19.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 20.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 19.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 20.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 20.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 21.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 20.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 21.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 21.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 22.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 21.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 22.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3274,7 +3274,7 @@
         <v>9</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.6069615796646161</v>
+        <v>0.6084500535640007</v>
       </c>
       <c r="J8" s="11" t="n">
         <v>0.2622673434856175</v>
@@ -3352,7 +3352,7 @@
         <v>7</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.5291363768537366</v>
+        <v>0.5274818261122419</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>-0.05539358600583089</v>
@@ -3430,7 +3430,7 @@
         <v>9</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>0.511</v>
+        <v>0.533</v>
       </c>
       <c r="J10" s="11" t="n">
         <v>0.05520169851380041</v>
@@ -3508,7 +3508,7 @@
         <v>9</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>0.484</v>
+        <v>0.489</v>
       </c>
       <c r="J11" s="17" t="n">
         <v>-0.002768439786434596</v>
@@ -3586,7 +3586,7 @@
         <v>9</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.547</v>
+        <v>0.5479999999999999</v>
       </c>
       <c r="J12" s="11" t="n">
         <v>0.07796862320800657</v>
@@ -3664,7 +3664,7 @@
         <v>9</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>0.5074919648808971</v>
+        <v>0.5088893478242525</v>
       </c>
       <c r="J13" s="17" t="n">
         <v>0.2563261480787253</v>
@@ -3742,7 +3742,7 @@
         <v>9</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.503</v>
+        <v>0.501</v>
       </c>
       <c r="J14" s="11" t="n">
         <v>0.01293841567831544</v>
@@ -3820,7 +3820,7 @@
         <v>9</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.4847728537985073</v>
+        <v>0.4863289886457418</v>
       </c>
       <c r="J15" s="17" t="n">
         <v>0.3372274143302181</v>
@@ -3898,7 +3898,7 @@
         <v>9</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>0.592</v>
+        <v>0.591</v>
       </c>
       <c r="J16" s="11" t="n">
         <v>-0.0553743056167887</v>
@@ -4054,7 +4054,7 @@
         <v>8</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>0.6394539263798517</v>
+        <v>0.6434746672951793</v>
       </c>
       <c r="J18" s="11" t="n">
         <v>0.3890274314214464</v>
@@ -4132,7 +4132,7 @@
         <v>9</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>0.5900553809176199</v>
+        <v>0.5999738812826111</v>
       </c>
       <c r="J19" s="17" t="n">
         <v>0.310091743119266</v>
@@ -4210,7 +4210,7 @@
         <v>9</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>0.598</v>
+        <v>0.5990000000000001</v>
       </c>
       <c r="J20" s="11" t="n">
         <v>0.004029880086494853</v>
@@ -4288,7 +4288,7 @@
         <v>9</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>0.573</v>
+        <v>0.5720000000000001</v>
       </c>
       <c r="J21" s="17" t="n">
         <v>0.4621775251421076</v>
@@ -4366,7 +4366,7 @@
         <v>9</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>0.6622496049554392</v>
+        <v>0.66983201651813</v>
       </c>
       <c r="J22" s="11" t="n">
         <v>0.05031810294968198</v>
@@ -4444,7 +4444,7 @@
         <v>9</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>0.5589999999999999</v>
+        <v>0.537</v>
       </c>
       <c r="J23" s="17" t="n">
         <v>0.2871178181246563</v>
@@ -4522,7 +4522,7 @@
         <v>9</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>0.5619999999999999</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="J24" s="11" t="n">
         <v>0.09250480461242816</v>
@@ -4678,7 +4678,7 @@
         <v>9</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.6423768930613507</v>
+        <v>0.6407180207850409</v>
       </c>
       <c r="J26" s="11" t="n">
         <v>0.322072072072072</v>
@@ -5146,7 +5146,7 @@
     <row r="38">
       <c r="A38" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 51%</t>
+          <t>Горячее · маржа 53%</t>
         </is>
       </c>
       <c r="B38" s="29" t="inlineStr">
@@ -5224,7 +5224,7 @@
     <row r="54">
       <c r="A54" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 48%</t>
+          <t>Горячее · маржа 49%</t>
         </is>
       </c>
       <c r="B54" s="29" t="inlineStr">
@@ -5536,7 +5536,7 @@
     <row r="118">
       <c r="A118" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 48%</t>
+          <t>Выпечка_ · маржа 49%</t>
         </is>
       </c>
       <c r="B118" s="29" t="inlineStr">
@@ -5848,7 +5848,7 @@
     <row r="182">
       <c r="A182" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 59%</t>
+          <t>Выпечка_ · маржа 60%</t>
         </is>
       </c>
       <c r="B182" s="29" t="inlineStr">
@@ -6082,7 +6082,7 @@
     <row r="230">
       <c r="A230" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 66%</t>
+          <t>Выпечка_ · маржа 67%</t>
         </is>
       </c>
       <c r="B230" s="29" t="inlineStr">
@@ -6160,7 +6160,7 @@
     <row r="246">
       <c r="A246" s="31" t="inlineStr">
         <is>
-          <t>СЭНДВИЧИ · маржа 56%</t>
+          <t>СЭНДВИЧИ · маржа 54%</t>
         </is>
       </c>
       <c r="B246" s="29" t="inlineStr">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 22.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 23.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 22.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 23.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3586,7 +3586,7 @@
         <v>9</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.5479999999999999</v>
+        <v>0.549</v>
       </c>
       <c r="J12" s="11" t="n">
         <v>0.07796862320800657</v>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 23.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 24.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
         <v>9</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.6084500535640007</v>
+        <v>0.6089462115304624</v>
       </c>
       <c r="J8" s="11" t="n">
         <v>0.2622673434856175</v>
@@ -4054,7 +4054,7 @@
         <v>8</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>0.6434746672951793</v>
+        <v>0.643876741386712</v>
       </c>
       <c r="J18" s="11" t="n">
         <v>0.3890274314214464</v>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 23.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 24.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 24.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 25.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
         <v>9</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.6089462115304624</v>
+        <v>0.6069615796646161</v>
       </c>
       <c r="J8" s="11" t="n">
         <v>0.2622673434856175</v>
@@ -3352,7 +3352,7 @@
         <v>7</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.5274818261122419</v>
+        <v>0.5283091014829893</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>-0.05539358600583089</v>
@@ -3664,7 +3664,7 @@
         <v>9</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>0.5088893478242525</v>
+        <v>0.5084235535098008</v>
       </c>
       <c r="J13" s="17" t="n">
         <v>0.2563261480787253</v>
@@ -3742,7 +3742,7 @@
         <v>9</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.501</v>
+        <v>0.503</v>
       </c>
       <c r="J14" s="11" t="n">
         <v>0.01293841567831544</v>
@@ -3820,7 +3820,7 @@
         <v>9</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.4863289886457418</v>
+        <v>0.4855509212221246</v>
       </c>
       <c r="J15" s="17" t="n">
         <v>0.3372274143302181</v>
@@ -4054,7 +4054,7 @@
         <v>8</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>0.643876741386712</v>
+        <v>0.6370414818306551</v>
       </c>
       <c r="J18" s="11" t="n">
         <v>0.3890274314214464</v>
@@ -4132,7 +4132,7 @@
         <v>9</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>0.5999738812826111</v>
+        <v>0.5900553809176199</v>
       </c>
       <c r="J19" s="17" t="n">
         <v>0.310091743119266</v>
@@ -4366,7 +4366,7 @@
         <v>9</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>0.66983201651813</v>
+        <v>0.6627912057813454</v>
       </c>
       <c r="J22" s="11" t="n">
         <v>0.05031810294968198</v>
@@ -4444,7 +4444,7 @@
         <v>9</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>0.537</v>
+        <v>0.5529999999999999</v>
       </c>
       <c r="J23" s="17" t="n">
         <v>0.2871178181246563</v>
@@ -4522,7 +4522,7 @@
         <v>9</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J24" s="11" t="n">
         <v>0.09250480461242816</v>
@@ -4678,7 +4678,7 @@
         <v>9</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.6407180207850409</v>
+        <v>0.6423768930613507</v>
       </c>
       <c r="J26" s="11" t="n">
         <v>0.322072072072072</v>
@@ -5848,7 +5848,7 @@
     <row r="182">
       <c r="A182" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 60%</t>
+          <t>Выпечка_ · маржа 59%</t>
         </is>
       </c>
       <c r="B182" s="29" t="inlineStr">
@@ -6082,7 +6082,7 @@
     <row r="230">
       <c r="A230" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 67%</t>
+          <t>Выпечка_ · маржа 66%</t>
         </is>
       </c>
       <c r="B230" s="29" t="inlineStr">
@@ -6160,7 +6160,7 @@
     <row r="246">
       <c r="A246" s="31" t="inlineStr">
         <is>
-          <t>СЭНДВИЧИ · маржа 54%</t>
+          <t>СЭНДВИЧИ · маржа 55%</t>
         </is>
       </c>
       <c r="B246" s="29" t="inlineStr">
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 24.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 25.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -1239,7 +1239,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Курица с сыром с пастой фузилли (1порц)</a:t>
+              <a:t>Сочник творожный (30шт гофра )</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1340,7 +1340,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Сочник творожный (30шт гофра )</a:t>
+              <a:t>Курица с сыром с пастой фузилли (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 25.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 26.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
         <v>9</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.6069615796646161</v>
+        <v>0.6089462115304624</v>
       </c>
       <c r="J8" s="11" t="n">
         <v>0.2622673434856175</v>
@@ -3337,13 +3337,13 @@
         </is>
       </c>
       <c r="D9" s="16" t="n">
-        <v>9170667</v>
+        <v>9164720</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>7076</v>
+        <v>7075</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>0.00286179319379154</v>
@@ -3352,10 +3352,10 @@
         <v>7</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.5283091014829893</v>
+        <v>0.527481489887307</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>-0.05539358600583089</v>
+        <v>-0.05587949465500497</v>
       </c>
       <c r="K9" s="17" t="n">
         <v>0.045</v>
@@ -3415,10 +3415,10 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>6024469</v>
+        <v>6018548</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>6792</v>
+        <v>6787</v>
       </c>
       <c r="F10" s="10" t="n">
         <v>887</v>
@@ -3433,7 +3433,7 @@
         <v>0.533</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>0.05520169851380041</v>
+        <v>0.05432137123919012</v>
       </c>
       <c r="K10" s="11" t="n">
         <v>0</v>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="D11" s="16" t="n">
-        <v>5427078</v>
+        <v>5417250</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>5043</v>
+        <v>5035</v>
       </c>
       <c r="F11" s="16" t="n">
         <v>1076</v>
@@ -3508,10 +3508,10 @@
         <v>9</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>0.489</v>
+        <v>0.4879999999999999</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>-0.002768439786434596</v>
+        <v>-0.00428449014567267</v>
       </c>
       <c r="K11" s="17" t="n">
         <v>0</v>
@@ -3571,25 +3571,25 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>5227594</v>
+        <v>5216361</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>5314</v>
+        <v>5304</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.1245748852020385</v>
+        <v>0.1234275707145103</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.549</v>
+        <v>0.547</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>0.07796862320800657</v>
+        <v>0.07600757370841227</v>
       </c>
       <c r="K12" s="11" t="n">
         <v>0</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="S12" s="14" t="inlineStr">
         <is>
-          <t>цену уже подняли на 12.5% — этого хватает</t>
+          <t>цену уже подняли на 12.3% — этого хватает</t>
         </is>
       </c>
       <c r="T12" s="14" t="inlineStr">
@@ -3664,7 +3664,7 @@
         <v>9</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>0.5084235535098008</v>
+        <v>0.5088893478242525</v>
       </c>
       <c r="J13" s="17" t="n">
         <v>0.2563261480787253</v>
@@ -3727,25 +3727,25 @@
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>4459789</v>
+        <v>4453418</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>5324</v>
+        <v>5317</v>
       </c>
       <c r="F14" s="10" t="n">
         <v>838</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.1162848266446101</v>
+        <v>0.1155114770278887</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.503</v>
+        <v>0.501</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>0.01293841567831544</v>
+        <v>0.01173336715925655</v>
       </c>
       <c r="K14" s="11" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>9</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.4855509212221246</v>
+        <v>0.4863289886457418</v>
       </c>
       <c r="J15" s="17" t="n">
         <v>0.3372274143302181</v>
@@ -3883,13 +3883,13 @@
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>4016334</v>
+        <v>4006632</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>3571</v>
+        <v>3564</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G16" s="11" t="n">
         <v>0.07968634845642675</v>
@@ -3898,10 +3898,10 @@
         <v>9</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>0.591</v>
+        <v>0.5910000000000001</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>-0.0553743056167887</v>
+        <v>-0.057314169826294</v>
       </c>
       <c r="K16" s="11" t="n">
         <v>0</v>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="D17" s="16" t="n">
-        <v>3600389</v>
+        <v>3589805</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="F17" s="16" t="n">
         <v>1103</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.08140582676728837</v>
+        <v>0.07972638213797945</v>
       </c>
       <c r="H17" s="18" t="n">
         <v>9</v>
@@ -3979,7 +3979,7 @@
         <v>0.597</v>
       </c>
       <c r="J17" s="17" t="n">
-        <v>-0.03374777975133214</v>
+        <v>-0.03611604499703969</v>
       </c>
       <c r="K17" s="17" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
         <v>8</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>0.6370414818306551</v>
+        <v>0.643876741386712</v>
       </c>
       <c r="J18" s="11" t="n">
         <v>0.3890274314214464</v>
@@ -4117,13 +4117,13 @@
         </is>
       </c>
       <c r="D19" s="16" t="n">
-        <v>3348939</v>
+        <v>3345829</v>
       </c>
       <c r="E19" s="16" t="n">
         <v>476</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>7036</v>
+        <v>7034</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>0.01803067648812484</v>
@@ -4132,10 +4132,10 @@
         <v>9</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>0.5900553809176199</v>
+        <v>0.5994927428057697</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>0.310091743119266</v>
+        <v>0.3091743119266057</v>
       </c>
       <c r="K19" s="17" t="n">
         <v>0.055</v>
@@ -4195,13 +4195,13 @@
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>3128263</v>
+        <v>3121956</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>3405</v>
+        <v>3399</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="G20" s="11" t="n">
         <v>0.1717550647996697</v>
@@ -4210,10 +4210,10 @@
         <v>9</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>0.5990000000000001</v>
+        <v>0.5989999999999999</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>0.004029880086494853</v>
+        <v>0.002358954196972629</v>
       </c>
       <c r="K20" s="11" t="n">
         <v>0</v>
@@ -4273,13 +4273,13 @@
         </is>
       </c>
       <c r="D21" s="16" t="n">
-        <v>3055830</v>
+        <v>3043884</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>3344</v>
+        <v>3334</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>0.06280981995184831</v>
@@ -4288,10 +4288,10 @@
         <v>9</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.572</v>
       </c>
       <c r="J21" s="17" t="n">
-        <v>0.4621775251421076</v>
+        <v>0.4576592333479084</v>
       </c>
       <c r="K21" s="17" t="n">
         <v>0.015</v>
@@ -4366,7 +4366,7 @@
         <v>9</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>0.6627912057813454</v>
+        <v>0.667665613214504</v>
       </c>
       <c r="J22" s="11" t="n">
         <v>0.05031810294968198</v>
@@ -4429,25 +4429,25 @@
         </is>
       </c>
       <c r="D23" s="16" t="n">
-        <v>2838135</v>
+        <v>2834913</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>5459</v>
+        <v>5453</v>
       </c>
       <c r="F23" s="16" t="n">
         <v>520</v>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.06105728642384234</v>
+        <v>0.06056258554386784</v>
       </c>
       <c r="H23" s="18" t="n">
         <v>9</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>0.5529999999999999</v>
+        <v>0.537</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>0.2871178181246563</v>
+        <v>0.2858602530849641</v>
       </c>
       <c r="K23" s="17" t="n">
         <v>0</v>
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2697686</v>
+        <v>2696301</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="F24" s="10" t="n">
         <v>949</v>
@@ -4522,10 +4522,10 @@
         <v>9</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>0.09250480461242816</v>
+        <v>0.09199231262011542</v>
       </c>
       <c r="K24" s="11" t="n">
         <v>0</v>
@@ -4571,45 +4571,45 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>Курица с сыром с пастой фузилли (1порц)</t>
+          <t>Сочник творожный (30шт гофра )</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Горячее</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>— не трогать</t>
+          <t>Выпечка_</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>2 — следом + 2-й шаг</t>
         </is>
       </c>
       <c r="D25" s="16" t="n">
-        <v>2693063</v>
+        <v>2691936</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>2475</v>
+        <v>391</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>1088</v>
+        <v>6879</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.06349256328931974</v>
+        <v>-0.01415503666138584</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>9</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.582</v>
+        <v>0.6407180207850409</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.05258681785967423</v>
+        <v>0.322072072072072</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="M25" s="16">
         <f>ROUND(F25*(1+L25),0)</f>
@@ -4637,57 +4637,57 @@
       </c>
       <c r="S25" s="19" t="inlineStr">
         <is>
-          <t>признаков отставания цены нет</t>
+          <t>за 9 мес цена упала на 1.4% при ориентире 6.0%; берут на 32% больше. Расчёт просит 9.0% — остальное вторым шагом через квартал</t>
         </is>
       </c>
       <c r="T25" s="19" t="inlineStr">
         <is>
-          <t>Упак Курица с сыром с пастой фузилли (1порц)</t>
+          <t>Упак Сочник творожный готов СМ (30шт гофра ) · RP* Упак Сочник творожный готов СМ (30шт гофра )</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Сочник творожный (30шт гофра )</t>
+          <t>Курица с сыром с пастой фузилли (1порц)</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Выпечка_</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
-        <is>
-          <t>2 — следом + 2-й шаг</t>
+          <t>Горячее</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>— не трогать</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2691936</v>
+        <v>2686448</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>391</v>
+        <v>2470</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>6879</v>
+        <v>1087</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>-0.01415503666138584</v>
+        <v>0.06342124528749893</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.6423768930613507</v>
+        <v>0.582</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>0.322072072072072</v>
+        <v>0.05046066619418865</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="M26" s="10">
         <f>ROUND(F26*(1+L26),0)</f>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="S26" s="14" t="inlineStr">
         <is>
-          <t>за 9 мес цена упала на 1.4% при ориентире 6.0%; берут на 32% больше. Расчёт просит 9.0% — остальное вторым шагом через квартал</t>
+          <t>признаков отставания цены нет</t>
         </is>
       </c>
       <c r="T26" s="14" t="inlineStr">
         <is>
-          <t>Упак Сочник творожный готов СМ (30шт гофра ) · RP* Упак Сочник творожный готов СМ (30шт гофра )</t>
+          <t>Упак Курица с сыром с пастой фузилли (1порц)</t>
         </is>
       </c>
     </row>
@@ -4741,16 +4741,16 @@
         </is>
       </c>
       <c r="D27" s="16" t="n">
-        <v>2687470</v>
+        <v>2678209</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>2530</v>
+        <v>2523</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.1152577075384189</v>
+        <v>0.1132783657521051</v>
       </c>
       <c r="H27" s="18" t="n">
         <v>9</v>
@@ -4759,7 +4759,7 @@
         <v>0.605</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>0.34377765976279</v>
+        <v>0.3400601876438309</v>
       </c>
       <c r="K27" s="17" t="n">
         <v>0</v>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="S27" s="19" t="inlineStr">
         <is>
-          <t>цену уже подняли на 11.5% — этого хватает</t>
+          <t>цену уже подняли на 11.3% — этого хватает</t>
         </is>
       </c>
       <c r="T27" s="19" t="inlineStr">
@@ -5062,7 +5062,7 @@
         <v>7012</v>
       </c>
       <c r="K21" s="30" t="n">
-        <v>7261</v>
+        <v>7256</v>
       </c>
     </row>
     <row r="22">
@@ -5101,7 +5101,7 @@
         <v>2456</v>
       </c>
       <c r="K22" s="32" t="n">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="37">
@@ -5179,7 +5179,7 @@
         <v>7265</v>
       </c>
       <c r="K38" s="32" t="n">
-        <v>6304</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="53">
@@ -5218,7 +5218,7 @@
         <v>1082</v>
       </c>
       <c r="K53" s="30" t="n">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="54">
@@ -5257,7 +5257,7 @@
         <v>5387</v>
       </c>
       <c r="K54" s="32" t="n">
-        <v>4821</v>
+        <v>4798</v>
       </c>
     </row>
     <row r="69">
@@ -5296,7 +5296,7 @@
         <v>1002</v>
       </c>
       <c r="K69" s="30" t="n">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="70">
@@ -5335,7 +5335,7 @@
         <v>5347</v>
       </c>
       <c r="K70" s="32" t="n">
-        <v>5337</v>
+        <v>5308</v>
       </c>
     </row>
     <row r="85">
@@ -5452,7 +5452,7 @@
         <v>853</v>
       </c>
       <c r="K101" s="30" t="n">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="102">
@@ -5491,7 +5491,7 @@
         <v>5267</v>
       </c>
       <c r="K102" s="32" t="n">
-        <v>5516</v>
+        <v>5497</v>
       </c>
     </row>
     <row r="117">
@@ -5608,7 +5608,7 @@
         <v>1137</v>
       </c>
       <c r="K133" s="30" t="n">
-        <v>1113</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="134">
@@ -5647,7 +5647,7 @@
         <v>3534</v>
       </c>
       <c r="K134" s="32" t="n">
-        <v>3570</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="149">
@@ -5686,7 +5686,7 @@
         <v>1115</v>
       </c>
       <c r="K149" s="30" t="n">
-        <v>1103</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="150">
@@ -5725,7 +5725,7 @@
         <v>3185</v>
       </c>
       <c r="K150" s="32" t="n">
-        <v>3106</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="165">
@@ -5842,13 +5842,13 @@
         <v>6946</v>
       </c>
       <c r="K181" s="30" t="n">
-        <v>6890</v>
+        <v>6884</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 59%</t>
+          <t>Выпечка_ · маржа 60%</t>
         </is>
       </c>
       <c r="B182" s="29" t="inlineStr">
@@ -5881,7 +5881,7 @@
         <v>444</v>
       </c>
       <c r="K182" s="32" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="197">
@@ -5920,7 +5920,7 @@
         <v>939</v>
       </c>
       <c r="K197" s="30" t="n">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="198">
@@ -5959,7 +5959,7 @@
         <v>3453</v>
       </c>
       <c r="K198" s="32" t="n">
-        <v>3528</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="213">
@@ -5998,7 +5998,7 @@
         <v>911</v>
       </c>
       <c r="K213" s="30" t="n">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="214">
@@ -6037,7 +6037,7 @@
         <v>3372</v>
       </c>
       <c r="K214" s="32" t="n">
-        <v>3897</v>
+        <v>3866</v>
       </c>
     </row>
     <row r="229">
@@ -6082,7 +6082,7 @@
     <row r="230">
       <c r="A230" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 66%</t>
+          <t>Выпечка_ · маржа 67%</t>
         </is>
       </c>
       <c r="B230" s="29" t="inlineStr">
@@ -6160,7 +6160,7 @@
     <row r="246">
       <c r="A246" s="31" t="inlineStr">
         <is>
-          <t>СЭНДВИЧИ · маржа 55%</t>
+          <t>СЭНДВИЧИ · маржа 54%</t>
         </is>
       </c>
       <c r="B246" s="29" t="inlineStr">
@@ -6193,7 +6193,7 @@
         <v>5713</v>
       </c>
       <c r="K246" s="32" t="n">
-        <v>5612</v>
+        <v>5596</v>
       </c>
     </row>
     <row r="261">
@@ -6271,13 +6271,13 @@
         <v>2945</v>
       </c>
       <c r="K262" s="32" t="n">
-        <v>2750</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="28" t="inlineStr">
         <is>
-          <t>Курица с сыром с пастой фузилли (1порц)</t>
+          <t>Сочник творожный (30шт гофра )</t>
         </is>
       </c>
       <c r="B277" s="29" t="inlineStr">
@@ -6286,37 +6286,37 @@
         </is>
       </c>
       <c r="C277" s="30" t="n">
-        <v>1032</v>
+        <v>7012</v>
       </c>
       <c r="D277" s="30" t="n">
-        <v>1031</v>
+        <v>6983</v>
       </c>
       <c r="E277" s="30" t="n">
-        <v>1074</v>
+        <v>7182</v>
       </c>
       <c r="F277" s="30" t="n">
-        <v>1048</v>
+        <v>7137</v>
       </c>
       <c r="G277" s="30" t="n">
-        <v>1066</v>
+        <v>7249</v>
       </c>
       <c r="H277" s="30" t="n">
-        <v>1006</v>
+        <v>6963</v>
       </c>
       <c r="I277" s="30" t="n">
-        <v>1065</v>
+        <v>6912</v>
       </c>
       <c r="J277" s="30" t="n">
-        <v>1097</v>
+        <v>6814</v>
       </c>
       <c r="K277" s="30" t="n">
-        <v>1099</v>
+        <v>6932</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 58%</t>
+          <t>Выпечка_ · маржа 64%</t>
         </is>
       </c>
       <c r="B278" s="29" t="inlineStr">
@@ -6325,37 +6325,37 @@
         </is>
       </c>
       <c r="C278" s="32" t="n">
-        <v>2109</v>
+        <v>210</v>
       </c>
       <c r="D278" s="32" t="n">
-        <v>1993</v>
+        <v>169</v>
       </c>
       <c r="E278" s="32" t="n">
-        <v>2249</v>
+        <v>231</v>
       </c>
       <c r="F278" s="32" t="n">
-        <v>2438</v>
+        <v>306</v>
       </c>
       <c r="G278" s="32" t="n">
-        <v>2252</v>
+        <v>235</v>
       </c>
       <c r="H278" s="32" t="n">
-        <v>2365</v>
+        <v>347</v>
       </c>
       <c r="I278" s="32" t="n">
-        <v>2244</v>
+        <v>418</v>
       </c>
       <c r="J278" s="32" t="n">
-        <v>2571</v>
+        <v>461</v>
       </c>
       <c r="K278" s="32" t="n">
-        <v>2611</v>
+        <v>295</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="28" t="inlineStr">
         <is>
-          <t>Сочник творожный (30шт гофра )</t>
+          <t>Курица с сыром с пастой фузилли (1порц)</t>
         </is>
       </c>
       <c r="B293" s="29" t="inlineStr">
@@ -6364,37 +6364,37 @@
         </is>
       </c>
       <c r="C293" s="30" t="n">
-        <v>7012</v>
+        <v>1032</v>
       </c>
       <c r="D293" s="30" t="n">
-        <v>6983</v>
+        <v>1031</v>
       </c>
       <c r="E293" s="30" t="n">
-        <v>7182</v>
+        <v>1074</v>
       </c>
       <c r="F293" s="30" t="n">
-        <v>7137</v>
+        <v>1048</v>
       </c>
       <c r="G293" s="30" t="n">
-        <v>7249</v>
+        <v>1066</v>
       </c>
       <c r="H293" s="30" t="n">
-        <v>6963</v>
+        <v>1006</v>
       </c>
       <c r="I293" s="30" t="n">
-        <v>6912</v>
+        <v>1065</v>
       </c>
       <c r="J293" s="30" t="n">
-        <v>6814</v>
+        <v>1097</v>
       </c>
       <c r="K293" s="30" t="n">
-        <v>6932</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 64%</t>
+          <t>Горячее · маржа 58%</t>
         </is>
       </c>
       <c r="B294" s="29" t="inlineStr">
@@ -6403,31 +6403,31 @@
         </is>
       </c>
       <c r="C294" s="32" t="n">
-        <v>210</v>
+        <v>2109</v>
       </c>
       <c r="D294" s="32" t="n">
-        <v>169</v>
+        <v>1993</v>
       </c>
       <c r="E294" s="32" t="n">
-        <v>231</v>
+        <v>2249</v>
       </c>
       <c r="F294" s="32" t="n">
-        <v>306</v>
+        <v>2438</v>
       </c>
       <c r="G294" s="32" t="n">
-        <v>235</v>
+        <v>2252</v>
       </c>
       <c r="H294" s="32" t="n">
-        <v>347</v>
+        <v>2365</v>
       </c>
       <c r="I294" s="32" t="n">
-        <v>418</v>
+        <v>2244</v>
       </c>
       <c r="J294" s="32" t="n">
-        <v>461</v>
+        <v>2571</v>
       </c>
       <c r="K294" s="32" t="n">
-        <v>295</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="309">
@@ -6466,7 +6466,7 @@
         <v>1082</v>
       </c>
       <c r="K309" s="30" t="n">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="310">
@@ -6505,7 +6505,7 @@
         <v>2484</v>
       </c>
       <c r="K310" s="32" t="n">
-        <v>2841</v>
+        <v>2820</v>
       </c>
     </row>
   </sheetData>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 25.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 26.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 26.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 27.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 26.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 27.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3586,7 +3586,7 @@
         <v>9</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.547</v>
+        <v>0.5479999999999999</v>
       </c>
       <c r="J12" s="11" t="n">
         <v>0.07600757370841227</v>
@@ -4522,7 +4522,7 @@
         <v>9</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5579999999999999</v>
       </c>
       <c r="J24" s="11" t="n">
         <v>0.09199231262011542</v>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 27.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 28.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 27.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 28.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3352,7 +3352,7 @@
         <v>7</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.527481489887307</v>
+        <v>0.528308653183076</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>-0.05587949465500497</v>
@@ -3508,7 +3508,7 @@
         <v>9</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>0.4879999999999999</v>
+        <v>0.485</v>
       </c>
       <c r="J11" s="17" t="n">
         <v>-0.00428449014567267</v>
@@ -3664,7 +3664,7 @@
         <v>9</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>0.5088893478242525</v>
+        <v>0.5084235535098008</v>
       </c>
       <c r="J13" s="17" t="n">
         <v>0.2563261480787253</v>
@@ -3742,7 +3742,7 @@
         <v>9</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.501</v>
+        <v>0.5029999999999999</v>
       </c>
       <c r="J14" s="11" t="n">
         <v>0.01173336715925655</v>
@@ -4132,7 +4132,7 @@
         <v>9</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>0.5994927428057697</v>
+        <v>0.5900563619104701</v>
       </c>
       <c r="J19" s="17" t="n">
         <v>0.3091743119266057</v>
@@ -4366,7 +4366,7 @@
         <v>9</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>0.667665613214504</v>
+        <v>0.6627912057813454</v>
       </c>
       <c r="J22" s="11" t="n">
         <v>0.05031810294968198</v>
@@ -4444,7 +4444,7 @@
         <v>9</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>0.537</v>
+        <v>0.5529999999999999</v>
       </c>
       <c r="J23" s="17" t="n">
         <v>0.2858602530849641</v>
@@ -4522,7 +4522,7 @@
         <v>9</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>0.5579999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J24" s="11" t="n">
         <v>0.09199231262011542</v>
@@ -4600,7 +4600,7 @@
         <v>9</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.6407180207850409</v>
+        <v>0.6423768930613507</v>
       </c>
       <c r="J25" s="17" t="n">
         <v>0.322072072072072</v>
@@ -5224,7 +5224,7 @@
     <row r="54">
       <c r="A54" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 49%</t>
+          <t>Горячее · маржа 48%</t>
         </is>
       </c>
       <c r="B54" s="29" t="inlineStr">
@@ -5848,7 +5848,7 @@
     <row r="182">
       <c r="A182" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 60%</t>
+          <t>Выпечка_ · маржа 59%</t>
         </is>
       </c>
       <c r="B182" s="29" t="inlineStr">
@@ -6082,7 +6082,7 @@
     <row r="230">
       <c r="A230" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 67%</t>
+          <t>Выпечка_ · маржа 66%</t>
         </is>
       </c>
       <c r="B230" s="29" t="inlineStr">
@@ -6160,7 +6160,7 @@
     <row r="246">
       <c r="A246" s="31" t="inlineStr">
         <is>
-          <t>СЭНДВИЧИ · маржа 54%</t>
+          <t>СЭНДВИЧИ · маржа 55%</t>
         </is>
       </c>
       <c r="B246" s="29" t="inlineStr">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 28.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 29.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 28.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 29.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 29.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 30.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 29.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 30.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 30.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 31.10.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 30.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 31.10.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>
